--- a/DadosProducao.xlsx
+++ b/DadosProducao.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.andrade\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{113ADB9C-CD37-4C91-A4C2-134B349713B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5988004-E360-452C-993D-68757E56D6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16284" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
   </bookViews>
   <sheets>
     <sheet name="DadosBrutos" sheetId="1" r:id="rId1"/>
     <sheet name="LimpezaDados" sheetId="2" r:id="rId2"/>
+    <sheet name="DadosBacklogXSaudavel" sheetId="3" r:id="rId3"/>
+    <sheet name="DadosFaturamento" sheetId="4" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +63,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -83,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3007" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3010" uniqueCount="109">
   <si>
     <t>PV</t>
   </si>
@@ -402,12 +404,22 @@
   <si>
     <t>Quantidade</t>
   </si>
+  <si>
+    <t>Saudavel</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>Vlr Faturado</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
@@ -511,16 +523,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -687,10 +700,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -731,17 +745,19 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="11">
     <dxf>
       <font>
         <b/>
@@ -883,16 +899,6 @@
             <color rgb="FFFFC000"/>
           </stop>
         </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
       </fill>
     </dxf>
     <dxf>
@@ -50418,4 +50424,4560 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76D838BA-A018-4D6D-9819-6D56600DF965}">
+  <dimension ref="A1:C727"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="str" cm="1">
+        <f t="array" ref="A1:A11">_xlfn.UNIQUE(DadosBrutos!C1:C727)</f>
+        <v>DATA</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B2">
+        <f>COUNTIFS(DadosBrutos!C:C, A2, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <f>COUNTIFS(DadosBrutos!C:C, A2, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="24">
+        <v>46303</v>
+      </c>
+      <c r="B3">
+        <f>COUNTIFS(DadosBrutos!C:C, A3, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>40</v>
+      </c>
+      <c r="C3">
+        <f>COUNTIFS(DadosBrutos!C:C, A3, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="24">
+        <v>46302</v>
+      </c>
+      <c r="B4">
+        <f>COUNTIFS(DadosBrutos!C:C, A4, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <f>COUNTIFS(DadosBrutos!C:C, A4, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <v>46308</v>
+      </c>
+      <c r="B5">
+        <f>COUNTIFS(DadosBrutos!C:C, A5, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>89</v>
+      </c>
+      <c r="C5">
+        <f>COUNTIFS(DadosBrutos!C:C, A5, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="24">
+        <v>46311</v>
+      </c>
+      <c r="B6">
+        <f>COUNTIFS(DadosBrutos!C:C, A6, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <f>COUNTIFS(DadosBrutos!C:C, A6, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="24">
+        <v>46307</v>
+      </c>
+      <c r="B7">
+        <f>COUNTIFS(DadosBrutos!C:C, A7, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <f>COUNTIFS(DadosBrutos!C:C, A7, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <v>46306</v>
+      </c>
+      <c r="B8">
+        <f>COUNTIFS(DadosBrutos!C:C, A8, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <f>COUNTIFS(DadosBrutos!C:C, A8, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="24">
+        <v>46305</v>
+      </c>
+      <c r="B9">
+        <f>COUNTIFS(DadosBrutos!C:C, A9, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <f>COUNTIFS(DadosBrutos!C:C, A9, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="24">
+        <v>46309</v>
+      </c>
+      <c r="B10">
+        <f>COUNTIFS(DadosBrutos!C:C, A10, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>22</v>
+      </c>
+      <c r="C10">
+        <f>COUNTIFS(DadosBrutos!C:C, A10, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="24">
+        <v>46310</v>
+      </c>
+      <c r="B11">
+        <f>COUNTIFS(DadosBrutos!C:C, A11, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>47</v>
+      </c>
+      <c r="C11">
+        <f>COUNTIFS(DadosBrutos!C:C, A11, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="24"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="24"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="24"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="24"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="24"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="24"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="24"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="24"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="24"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="24"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="24"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="24"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="24"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="24"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="24"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="24"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="24"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="24"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="24"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="24"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="24"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="24"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="24"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="24"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="24"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="24"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="24"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="24"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="24"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="24"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="24"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="24"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="24"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="24"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="24"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="24"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="24"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="24"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="24"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="24"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="24"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="24"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="24"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="24"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="24"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="24"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="24"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="24"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="24"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="24"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="24"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="24"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="24"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="24"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="24"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="24"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="24"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="24"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="24"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="24"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="24"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="24"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="24"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="24"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="24"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="24"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="24"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="24"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="24"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="24"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="24"/>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="24"/>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="24"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="24"/>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="24"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="24"/>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="24"/>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="24"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="24"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="24"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="24"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="24"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="24"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="24"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="24"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="24"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="24"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="24"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="24"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="24"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="24"/>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="24"/>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="24"/>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="24"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="24"/>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="24"/>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="24"/>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="24"/>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="24"/>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="24"/>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="24"/>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="24"/>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="24"/>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="24"/>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="24"/>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="24"/>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="24"/>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="24"/>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="24"/>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="24"/>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="24"/>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="24"/>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="24"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="24"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="24"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="24"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="24"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="24"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="24"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="24"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="24"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="24"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="24"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="24"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="24"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="24"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="24"/>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="24"/>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="24"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="24"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="24"/>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="24"/>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="24"/>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="24"/>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="24"/>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="24"/>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="24"/>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="24"/>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="24"/>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="24"/>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="24"/>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="24"/>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="24"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="24"/>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="24"/>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="24"/>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="24"/>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="24"/>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="24"/>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="24"/>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="24"/>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="24"/>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="24"/>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="24"/>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="24"/>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="24"/>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="24"/>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="24"/>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="24"/>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="24"/>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="24"/>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="24"/>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="24"/>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="24"/>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="24"/>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="24"/>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="24"/>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="24"/>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="24"/>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="24"/>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="24"/>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="24"/>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="24"/>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="24"/>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="24"/>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="24"/>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="24"/>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="24"/>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="24"/>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="24"/>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="24"/>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="24"/>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="24"/>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="24"/>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="24"/>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="24"/>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="24"/>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="24"/>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="24"/>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="24"/>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="24"/>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="24"/>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="24"/>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="24"/>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="24"/>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="24"/>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="24"/>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="24"/>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="24"/>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="24"/>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="24"/>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="24"/>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="24"/>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="24"/>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="24"/>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="24"/>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="24"/>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="24"/>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="24"/>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" s="24"/>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" s="24"/>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" s="24"/>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" s="24"/>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" s="24"/>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" s="24"/>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" s="24"/>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" s="24"/>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" s="24"/>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" s="24"/>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" s="24"/>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" s="24"/>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" s="24"/>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" s="24"/>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" s="24"/>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" s="24"/>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" s="24"/>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" s="24"/>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" s="24"/>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" s="24"/>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" s="24"/>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" s="24"/>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" s="24"/>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" s="24"/>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" s="24"/>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" s="24"/>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="24"/>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" s="24"/>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" s="24"/>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" s="24"/>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" s="24"/>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" s="24"/>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" s="24"/>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" s="24"/>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="24"/>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" s="24"/>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" s="24"/>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" s="24"/>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" s="24"/>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" s="24"/>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" s="24"/>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" s="24"/>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" s="24"/>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="24"/>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" s="24"/>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" s="24"/>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" s="24"/>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="24"/>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="24"/>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" s="24"/>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" s="24"/>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" s="24"/>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="24"/>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="24"/>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" s="24"/>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" s="24"/>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" s="24"/>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" s="24"/>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" s="24"/>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" s="24"/>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" s="24"/>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" s="24"/>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" s="24"/>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" s="24"/>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" s="24"/>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" s="24"/>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" s="24"/>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" s="24"/>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" s="24"/>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" s="24"/>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" s="24"/>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" s="24"/>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" s="24"/>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="24"/>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" s="24"/>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" s="24"/>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" s="24"/>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" s="24"/>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" s="24"/>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" s="24"/>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" s="24"/>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" s="24"/>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" s="24"/>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" s="24"/>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" s="24"/>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" s="24"/>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" s="24"/>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" s="24"/>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" s="24"/>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" s="24"/>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" s="24"/>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" s="24"/>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" s="24"/>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" s="24"/>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" s="24"/>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" s="24"/>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" s="24"/>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" s="24"/>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" s="24"/>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" s="24"/>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" s="24"/>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" s="24"/>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" s="24"/>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" s="24"/>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" s="24"/>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" s="24"/>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" s="24"/>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" s="24"/>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" s="24"/>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" s="24"/>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" s="24"/>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" s="24"/>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" s="24"/>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370" s="24"/>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371" s="24"/>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372" s="24"/>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373" s="24"/>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374" s="24"/>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375" s="24"/>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376" s="24"/>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377" s="24"/>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378" s="24"/>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379" s="24"/>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380" s="24"/>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381" s="24"/>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382" s="24"/>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383" s="24"/>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384" s="24"/>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385" s="24"/>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386" s="24"/>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" s="24"/>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388" s="24"/>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389" s="24"/>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390" s="24"/>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391" s="24"/>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392" s="24"/>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393" s="24"/>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394" s="24"/>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395" s="24"/>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396" s="24"/>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397" s="24"/>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398" s="24"/>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399" s="24"/>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400" s="24"/>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401" s="24"/>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402" s="24"/>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403" s="24"/>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404" s="24"/>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405" s="24"/>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406" s="24"/>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407" s="24"/>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408" s="24"/>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409" s="24"/>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410" s="24"/>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411" s="24"/>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412" s="24"/>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A413" s="24"/>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A414" s="24"/>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415" s="24"/>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416" s="24"/>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417" s="24"/>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418" s="24"/>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419" s="24"/>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420" s="24"/>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421" s="24"/>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422" s="24"/>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423" s="24"/>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424" s="24"/>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425" s="24"/>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426" s="24"/>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427" s="24"/>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428" s="24"/>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429" s="24"/>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430" s="24"/>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431" s="24"/>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432" s="24"/>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433" s="24"/>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434" s="24"/>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435" s="24"/>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A436" s="24"/>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A437" s="24"/>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A438" s="24"/>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A439" s="24"/>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A440" s="24"/>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A441" s="24"/>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A442" s="24"/>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A443" s="24"/>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A444" s="24"/>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A445" s="24"/>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A446" s="24"/>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A447" s="24"/>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A448" s="24"/>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A449" s="24"/>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A450" s="24"/>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A451" s="24"/>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A452" s="24"/>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A453" s="24"/>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A454" s="24"/>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A455" s="24"/>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A456" s="24"/>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A457" s="24"/>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A458" s="24"/>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A459" s="24"/>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A460" s="24"/>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A461" s="24"/>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A462" s="24"/>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A463" s="24"/>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A464" s="24"/>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A465" s="24"/>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A466" s="24"/>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A467" s="24"/>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A468" s="24"/>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A469" s="24"/>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A470" s="24"/>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A471" s="24"/>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A472" s="24"/>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A473" s="24"/>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A474" s="24"/>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A475" s="24"/>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A476" s="24"/>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A477" s="24"/>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A478" s="24"/>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A479" s="24"/>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A480" s="24"/>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A481" s="24"/>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A482" s="24"/>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A483" s="24"/>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A484" s="24"/>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A485" s="24"/>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A486" s="24"/>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A487" s="24"/>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A488" s="24"/>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A489" s="24"/>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A490" s="24"/>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A491" s="24"/>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A492" s="24"/>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A493" s="24"/>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A494" s="24"/>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A495" s="24"/>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A496" s="24"/>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A497" s="24"/>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A498" s="24"/>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A499" s="24"/>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A500" s="24"/>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A501" s="24"/>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A502" s="24"/>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A503" s="24"/>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A504" s="24"/>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A505" s="24"/>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A506" s="24"/>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A507" s="24"/>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A508" s="24"/>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A509" s="24"/>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A510" s="24"/>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A511" s="24"/>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A512" s="24"/>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A513" s="24"/>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A514" s="24"/>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A515" s="24"/>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A516" s="24"/>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A517" s="24"/>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A518" s="24"/>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A519" s="24"/>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A520" s="24"/>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A521" s="24"/>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A522" s="24"/>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A523" s="24"/>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A524" s="24"/>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A525" s="24"/>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A526" s="24"/>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A527" s="24"/>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A528" s="24"/>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A529" s="24"/>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A530" s="24"/>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A531" s="24"/>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A532" s="24"/>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A533" s="24"/>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A534" s="24"/>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A535" s="24"/>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A536" s="24"/>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A537" s="24"/>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A538" s="24"/>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A539" s="24"/>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A540" s="24"/>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A541" s="24"/>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A542" s="24"/>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A543" s="24"/>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A544" s="24"/>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A545" s="24"/>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A546" s="24"/>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A547" s="24"/>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A548" s="24"/>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A549" s="24"/>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A550" s="24"/>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A551" s="24"/>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A552" s="24"/>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A553" s="24"/>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A554" s="24"/>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A555" s="24"/>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A556" s="24"/>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A557" s="24"/>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A558" s="24"/>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A559" s="24"/>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A560" s="24"/>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A561" s="24"/>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A562" s="24"/>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A563" s="24"/>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A564" s="24"/>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A565" s="24"/>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A566" s="24"/>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A567" s="24"/>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A568" s="24"/>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A569" s="24"/>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A570" s="24"/>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A571" s="24"/>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A572" s="24"/>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A573" s="24"/>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A574" s="24"/>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A575" s="24"/>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A576" s="24"/>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A577" s="24"/>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A578" s="24"/>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A579" s="24"/>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A580" s="24"/>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A581" s="24"/>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A582" s="24"/>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A583" s="24"/>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A584" s="24"/>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A585" s="24"/>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A586" s="24"/>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A587" s="24"/>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A588" s="24"/>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A589" s="24"/>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A590" s="24"/>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A591" s="24"/>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A592" s="24"/>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A593" s="24"/>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A594" s="24"/>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A595" s="24"/>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A596" s="24"/>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A597" s="24"/>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A598" s="24"/>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A599" s="24"/>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A600" s="24"/>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A601" s="24"/>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A602" s="24"/>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A603" s="24"/>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A604" s="24"/>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A605" s="24"/>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A606" s="24"/>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A607" s="24"/>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A608" s="24"/>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A609" s="24"/>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A610" s="24"/>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A611" s="24"/>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A612" s="24"/>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A613" s="24"/>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A614" s="24"/>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A615" s="24"/>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A616" s="24"/>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A617" s="24"/>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A618" s="24"/>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A619" s="24"/>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A620" s="24"/>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A621" s="24"/>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A622" s="24"/>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A623" s="24"/>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A624" s="24"/>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A625" s="24"/>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A626" s="24"/>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A627" s="24"/>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A628" s="24"/>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A629" s="24"/>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A630" s="24"/>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A631" s="24"/>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A632" s="24"/>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A633" s="24"/>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A634" s="24"/>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A635" s="24"/>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A636" s="24"/>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A637" s="24"/>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A638" s="24"/>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A639" s="24"/>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A640" s="24"/>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A641" s="24"/>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A642" s="24"/>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A643" s="24"/>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A644" s="24"/>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A645" s="24"/>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A646" s="24"/>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A647" s="24"/>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A648" s="24"/>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A649" s="24"/>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A650" s="24"/>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A651" s="24"/>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A652" s="24"/>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A653" s="24"/>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A654" s="24"/>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A655" s="24"/>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A656" s="24"/>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A657" s="24"/>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A658" s="24"/>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A659" s="24"/>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A660" s="24"/>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A661" s="24"/>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A662" s="24"/>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A663" s="24"/>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A664" s="24"/>
+    </row>
+    <row r="665" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A665" s="24"/>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A666" s="24"/>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A667" s="24"/>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A668" s="24"/>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A669" s="24"/>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A670" s="24"/>
+    </row>
+    <row r="671" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A671" s="24"/>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A672" s="24"/>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A673" s="24"/>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A674" s="24"/>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A675" s="24"/>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A676" s="24"/>
+    </row>
+    <row r="677" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A677" s="24"/>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A678" s="24"/>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A679" s="24"/>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A680" s="24"/>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A681" s="24"/>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A682" s="24"/>
+    </row>
+    <row r="683" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A683" s="24"/>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A684" s="24"/>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A685" s="25"/>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A686" s="25"/>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A687" s="25"/>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A688" s="25"/>
+    </row>
+    <row r="689" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A689" s="25"/>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A690" s="25"/>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A691" s="25"/>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A692" s="25"/>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A693" s="25"/>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A694" s="25"/>
+    </row>
+    <row r="695" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A695" s="25"/>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A696" s="25"/>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A697" s="25"/>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A698" s="25"/>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A699" s="25"/>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A700" s="25"/>
+    </row>
+    <row r="701" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A701" s="25"/>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A702" s="25"/>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A703" s="25"/>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A704" s="25"/>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A705" s="25"/>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A706" s="25"/>
+    </row>
+    <row r="707" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A707" s="25"/>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A708" s="25"/>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A709" s="25"/>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A710" s="25"/>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A711" s="25"/>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A712" s="25"/>
+    </row>
+    <row r="713" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A713" s="25"/>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A714" s="25"/>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A715" s="25"/>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A716" s="25"/>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A717" s="25"/>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A718" s="25"/>
+    </row>
+    <row r="719" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A719" s="25"/>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A720" s="25"/>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A721" s="25"/>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A722" s="25"/>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A723" s="25"/>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A724" s="25"/>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A725" s="25"/>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A726" s="25"/>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A727" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A8FB21-A1F8-40C7-9CA7-CA07CB9FFF27}">
+  <dimension ref="A1:B727"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="str" cm="1">
+        <f t="array" ref="A1:A11">_xlfn.UNIQUE(DadosBrutos!C1:C727)</f>
+        <v>DATA</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B2" s="26">
+        <v>323204.13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="24">
+        <v>46303</v>
+      </c>
+      <c r="B3" s="26">
+        <v>766597.26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="24">
+        <v>46302</v>
+      </c>
+      <c r="B4" s="26">
+        <v>322663.09000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <v>46308</v>
+      </c>
+      <c r="B5" s="26">
+        <v>476395.59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="24">
+        <v>46311</v>
+      </c>
+      <c r="B6" s="26">
+        <v>1395331.97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="24">
+        <v>46307</v>
+      </c>
+      <c r="B7" s="26">
+        <v>216275.07</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <v>46306</v>
+      </c>
+      <c r="B8" s="26">
+        <v>203448.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="24">
+        <v>46305</v>
+      </c>
+      <c r="B9" s="26">
+        <v>218825.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="24">
+        <v>46309</v>
+      </c>
+      <c r="B10" s="26">
+        <v>329456.51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="24">
+        <v>46310</v>
+      </c>
+      <c r="B11" s="26">
+        <v>300180.06</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="24"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="24"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="24"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="24"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="24"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="24"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="24"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="24"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="24"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="24"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="24"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="24"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="24"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="24"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="24"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="24"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="24"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="24"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="24"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="24"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="24"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="24"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="24"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="24"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="24"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="24"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="24"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="24"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="24"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="24"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="24"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="24"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="24"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="24"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="24"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="24"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="24"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="24"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="24"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="24"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="24"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="24"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="24"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="24"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="24"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="24"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="24"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="24"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="24"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="24"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="24"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="24"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="24"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="24"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="24"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="24"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="24"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="24"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="24"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="24"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="24"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="24"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="24"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="24"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="24"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="24"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="24"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="24"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="24"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="24"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="24"/>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="24"/>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="24"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="24"/>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="24"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="24"/>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="24"/>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="24"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="24"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="24"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="24"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="24"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="24"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="24"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="24"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="24"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="24"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="24"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="24"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="24"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="24"/>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="24"/>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="24"/>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="24"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="24"/>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="24"/>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="24"/>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="24"/>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="24"/>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="24"/>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="24"/>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="24"/>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="24"/>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="24"/>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="24"/>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="24"/>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="24"/>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="24"/>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="24"/>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="24"/>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="24"/>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="24"/>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="24"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="24"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="24"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="24"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="24"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="24"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="24"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="24"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="24"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="24"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="24"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="24"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="24"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="24"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="24"/>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="24"/>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="24"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="24"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="24"/>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="24"/>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="24"/>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="24"/>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="24"/>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="24"/>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="24"/>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="24"/>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="24"/>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="24"/>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="24"/>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="24"/>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="24"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="24"/>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="24"/>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="24"/>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="24"/>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="24"/>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="24"/>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="24"/>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="24"/>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="24"/>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="24"/>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="24"/>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="24"/>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="24"/>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="24"/>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="24"/>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="24"/>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="24"/>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="24"/>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="24"/>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="24"/>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="24"/>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="24"/>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="24"/>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="24"/>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="24"/>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="24"/>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="24"/>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="24"/>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="24"/>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="24"/>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="24"/>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="24"/>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="24"/>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="24"/>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="24"/>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="24"/>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="24"/>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="24"/>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="24"/>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="24"/>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="24"/>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="24"/>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="24"/>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="24"/>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="24"/>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="24"/>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="24"/>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="24"/>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="24"/>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="24"/>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="24"/>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="24"/>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="24"/>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="24"/>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="24"/>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="24"/>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="24"/>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="24"/>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="24"/>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="24"/>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="24"/>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="24"/>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="24"/>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="24"/>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="24"/>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="24"/>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" s="24"/>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" s="24"/>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" s="24"/>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" s="24"/>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" s="24"/>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" s="24"/>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" s="24"/>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" s="24"/>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" s="24"/>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" s="24"/>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" s="24"/>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" s="24"/>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" s="24"/>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" s="24"/>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" s="24"/>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" s="24"/>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" s="24"/>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" s="24"/>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" s="24"/>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" s="24"/>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" s="24"/>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" s="24"/>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" s="24"/>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" s="24"/>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" s="24"/>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" s="24"/>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="24"/>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" s="24"/>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" s="24"/>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" s="24"/>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" s="24"/>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" s="24"/>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" s="24"/>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" s="24"/>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="24"/>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" s="24"/>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" s="24"/>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" s="24"/>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" s="24"/>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" s="24"/>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" s="24"/>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" s="24"/>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" s="24"/>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="24"/>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" s="24"/>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" s="24"/>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" s="24"/>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="24"/>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="24"/>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" s="24"/>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" s="24"/>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" s="24"/>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="24"/>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="24"/>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" s="24"/>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" s="24"/>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" s="24"/>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" s="24"/>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" s="24"/>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" s="24"/>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" s="24"/>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" s="24"/>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" s="24"/>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" s="24"/>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" s="24"/>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" s="24"/>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" s="24"/>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" s="24"/>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" s="24"/>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" s="24"/>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" s="24"/>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" s="24"/>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" s="24"/>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="24"/>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" s="24"/>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" s="24"/>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" s="24"/>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" s="24"/>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" s="24"/>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" s="24"/>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" s="24"/>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" s="24"/>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" s="24"/>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" s="24"/>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" s="24"/>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" s="24"/>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" s="24"/>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" s="24"/>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" s="24"/>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" s="24"/>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" s="24"/>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" s="24"/>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" s="24"/>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" s="24"/>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" s="24"/>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" s="24"/>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" s="24"/>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" s="24"/>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" s="24"/>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" s="24"/>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" s="24"/>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" s="24"/>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" s="24"/>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" s="24"/>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" s="24"/>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" s="24"/>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" s="24"/>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" s="24"/>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" s="24"/>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" s="24"/>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" s="24"/>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" s="24"/>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" s="24"/>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370" s="24"/>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371" s="24"/>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372" s="24"/>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373" s="24"/>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374" s="24"/>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375" s="24"/>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376" s="24"/>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377" s="24"/>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378" s="24"/>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379" s="24"/>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380" s="24"/>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381" s="24"/>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382" s="24"/>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383" s="24"/>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384" s="24"/>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385" s="24"/>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386" s="24"/>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" s="24"/>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388" s="24"/>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389" s="24"/>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390" s="24"/>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391" s="24"/>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392" s="24"/>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393" s="24"/>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394" s="24"/>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395" s="24"/>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396" s="24"/>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397" s="24"/>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398" s="24"/>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399" s="24"/>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400" s="24"/>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401" s="24"/>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402" s="24"/>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403" s="24"/>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404" s="24"/>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405" s="24"/>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406" s="24"/>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407" s="24"/>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408" s="24"/>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409" s="24"/>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410" s="24"/>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411" s="24"/>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412" s="24"/>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A413" s="24"/>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A414" s="24"/>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415" s="24"/>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416" s="24"/>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417" s="24"/>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418" s="24"/>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419" s="24"/>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420" s="24"/>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421" s="24"/>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422" s="24"/>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423" s="24"/>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424" s="24"/>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425" s="24"/>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426" s="24"/>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427" s="24"/>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428" s="24"/>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429" s="24"/>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430" s="24"/>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431" s="24"/>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432" s="24"/>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433" s="24"/>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434" s="24"/>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435" s="24"/>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A436" s="24"/>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A437" s="24"/>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A438" s="24"/>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A439" s="24"/>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A440" s="24"/>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A441" s="24"/>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A442" s="24"/>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A443" s="24"/>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A444" s="24"/>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A445" s="24"/>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A446" s="24"/>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A447" s="24"/>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A448" s="24"/>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A449" s="24"/>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A450" s="24"/>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A451" s="24"/>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A452" s="24"/>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A453" s="24"/>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A454" s="24"/>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A455" s="24"/>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A456" s="24"/>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A457" s="24"/>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A458" s="24"/>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A459" s="24"/>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A460" s="24"/>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A461" s="24"/>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A462" s="24"/>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A463" s="24"/>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A464" s="24"/>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A465" s="24"/>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A466" s="24"/>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A467" s="24"/>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A468" s="24"/>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A469" s="24"/>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A470" s="24"/>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A471" s="24"/>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A472" s="24"/>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A473" s="24"/>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A474" s="24"/>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A475" s="24"/>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A476" s="24"/>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A477" s="24"/>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A478" s="24"/>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A479" s="24"/>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A480" s="24"/>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A481" s="24"/>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A482" s="24"/>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A483" s="24"/>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A484" s="24"/>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A485" s="24"/>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A486" s="24"/>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A487" s="24"/>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A488" s="24"/>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A489" s="24"/>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A490" s="24"/>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A491" s="24"/>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A492" s="24"/>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A493" s="24"/>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A494" s="24"/>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A495" s="24"/>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A496" s="24"/>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A497" s="24"/>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A498" s="24"/>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A499" s="24"/>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A500" s="24"/>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A501" s="24"/>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A502" s="24"/>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A503" s="24"/>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A504" s="24"/>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A505" s="24"/>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A506" s="24"/>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A507" s="24"/>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A508" s="24"/>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A509" s="24"/>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A510" s="24"/>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A511" s="24"/>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A512" s="24"/>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A513" s="24"/>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A514" s="24"/>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A515" s="24"/>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A516" s="24"/>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A517" s="24"/>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A518" s="24"/>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A519" s="24"/>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A520" s="24"/>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A521" s="24"/>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A522" s="24"/>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A523" s="24"/>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A524" s="24"/>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A525" s="24"/>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A526" s="24"/>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A527" s="24"/>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A528" s="24"/>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A529" s="24"/>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A530" s="24"/>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A531" s="24"/>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A532" s="24"/>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A533" s="24"/>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A534" s="24"/>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A535" s="24"/>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A536" s="24"/>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A537" s="24"/>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A538" s="24"/>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A539" s="24"/>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A540" s="24"/>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A541" s="24"/>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A542" s="24"/>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A543" s="24"/>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A544" s="24"/>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A545" s="24"/>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A546" s="24"/>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A547" s="24"/>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A548" s="24"/>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A549" s="24"/>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A550" s="24"/>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A551" s="24"/>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A552" s="24"/>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A553" s="24"/>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A554" s="24"/>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A555" s="24"/>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A556" s="24"/>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A557" s="24"/>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A558" s="24"/>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A559" s="24"/>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A560" s="24"/>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A561" s="24"/>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A562" s="24"/>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A563" s="24"/>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A564" s="24"/>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A565" s="24"/>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A566" s="24"/>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A567" s="24"/>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A568" s="24"/>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A569" s="24"/>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A570" s="24"/>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A571" s="24"/>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A572" s="24"/>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A573" s="24"/>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A574" s="24"/>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A575" s="24"/>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A576" s="24"/>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A577" s="24"/>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A578" s="24"/>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A579" s="24"/>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A580" s="24"/>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A581" s="24"/>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A582" s="24"/>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A583" s="24"/>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A584" s="24"/>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A585" s="24"/>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A586" s="24"/>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A587" s="24"/>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A588" s="24"/>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A589" s="24"/>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A590" s="24"/>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A591" s="24"/>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A592" s="24"/>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A593" s="24"/>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A594" s="24"/>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A595" s="24"/>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A596" s="24"/>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A597" s="24"/>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A598" s="24"/>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A599" s="24"/>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A600" s="24"/>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A601" s="24"/>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A602" s="24"/>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A603" s="24"/>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A604" s="24"/>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A605" s="24"/>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A606" s="24"/>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A607" s="24"/>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A608" s="24"/>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A609" s="24"/>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A610" s="24"/>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A611" s="24"/>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A612" s="24"/>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A613" s="24"/>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A614" s="24"/>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A615" s="24"/>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A616" s="24"/>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A617" s="24"/>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A618" s="24"/>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A619" s="24"/>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A620" s="24"/>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A621" s="24"/>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A622" s="24"/>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A623" s="24"/>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A624" s="24"/>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A625" s="24"/>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A626" s="24"/>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A627" s="24"/>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A628" s="24"/>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A629" s="24"/>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A630" s="24"/>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A631" s="24"/>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A632" s="24"/>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A633" s="24"/>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A634" s="24"/>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A635" s="24"/>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A636" s="24"/>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A637" s="24"/>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A638" s="24"/>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A639" s="24"/>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A640" s="24"/>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A641" s="24"/>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A642" s="24"/>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A643" s="24"/>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A644" s="24"/>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A645" s="24"/>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A646" s="24"/>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A647" s="24"/>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A648" s="24"/>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A649" s="24"/>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A650" s="24"/>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A651" s="24"/>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A652" s="24"/>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A653" s="24"/>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A654" s="24"/>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A655" s="24"/>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A656" s="24"/>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A657" s="24"/>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A658" s="24"/>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A659" s="24"/>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A660" s="24"/>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A661" s="24"/>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A662" s="24"/>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A663" s="24"/>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A664" s="24"/>
+    </row>
+    <row r="665" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A665" s="24"/>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A666" s="24"/>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A667" s="24"/>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A668" s="24"/>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A669" s="24"/>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A670" s="24"/>
+    </row>
+    <row r="671" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A671" s="24"/>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A672" s="24"/>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A673" s="24"/>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A674" s="24"/>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A675" s="24"/>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A676" s="24"/>
+    </row>
+    <row r="677" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A677" s="24"/>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A678" s="24"/>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A679" s="24"/>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A680" s="24"/>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A681" s="24"/>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A682" s="24"/>
+    </row>
+    <row r="683" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A683" s="24"/>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A684" s="24"/>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A685" s="25"/>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A686" s="25"/>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A687" s="25"/>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A688" s="25"/>
+    </row>
+    <row r="689" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A689" s="25"/>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A690" s="25"/>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A691" s="25"/>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A692" s="25"/>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A693" s="25"/>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A694" s="25"/>
+    </row>
+    <row r="695" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A695" s="25"/>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A696" s="25"/>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A697" s="25"/>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A698" s="25"/>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A699" s="25"/>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A700" s="25"/>
+    </row>
+    <row r="701" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A701" s="25"/>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A702" s="25"/>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A703" s="25"/>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A704" s="25"/>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A705" s="25"/>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A706" s="25"/>
+    </row>
+    <row r="707" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A707" s="25"/>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A708" s="25"/>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A709" s="25"/>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A710" s="25"/>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A711" s="25"/>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A712" s="25"/>
+    </row>
+    <row r="713" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A713" s="25"/>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A714" s="25"/>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A715" s="25"/>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A716" s="25"/>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A717" s="25"/>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A718" s="25"/>
+    </row>
+    <row r="719" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A719" s="25"/>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A720" s="25"/>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A721" s="25"/>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A722" s="25"/>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A723" s="25"/>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A724" s="25"/>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A725" s="25"/>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A726" s="25"/>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A727" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/DadosProducao.xlsx
+++ b/DadosProducao.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.andrade\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC15318-1ABC-41BB-9F1C-9E29621BE27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B88C92-47BB-4EF9-8034-4D8BFA9F9CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3691" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="154">
   <si>
     <t>PV</t>
   </si>
@@ -502,6 +502,51 @@
   <si>
     <t>DASA HOSP 9 DE JULHO</t>
   </si>
+  <si>
+    <t>GUIMA CONSECO</t>
+  </si>
+  <si>
+    <t>HOSP HELIOPOLIS</t>
+  </si>
+  <si>
+    <t>HOSP PROF EDMUNDO VA</t>
+  </si>
+  <si>
+    <t>BIOFAST</t>
+  </si>
+  <si>
+    <t>DRS XVI-SOROCABA</t>
+  </si>
+  <si>
+    <t>DASA LAB VALECLIN</t>
+  </si>
+  <si>
+    <t>DASA SALOMAO E ZOPPI</t>
+  </si>
+  <si>
+    <t>DASA DF</t>
+  </si>
+  <si>
+    <t>SAO CAMILO POMPEIA</t>
+  </si>
+  <si>
+    <t>DASA PQ DUQUE CAXIAS</t>
+  </si>
+  <si>
+    <t>SWISS PARK</t>
+  </si>
+  <si>
+    <t>COI CLINICA 39.086.1</t>
+  </si>
+  <si>
+    <t>ACALANTO CLINICA</t>
+  </si>
+  <si>
+    <t>DASA RECIFE 61.486.6</t>
+  </si>
+  <si>
+    <t>SECONCI HELIOPOLIS</t>
+  </si>
 </sst>
 </file>
 
@@ -851,9 +896,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28123,7 +28168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B0C76F-2D49-44D6-9EF1-05536D6E01AD}">
-  <dimension ref="A1:I875"/>
+  <dimension ref="A1:H935"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -48038,7 +48083,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="721" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" s="9">
         <v>69886</v>
       </c>
@@ -48064,7 +48109,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="722" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" s="9">
         <v>69861</v>
       </c>
@@ -48090,7 +48135,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="723" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" s="9">
         <v>69956</v>
       </c>
@@ -48116,7 +48161,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="724" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" s="9">
         <v>70015</v>
       </c>
@@ -48142,7 +48187,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="725" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" s="9">
         <v>69971</v>
       </c>
@@ -48168,7 +48213,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="726" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" s="9">
         <v>69551</v>
       </c>
@@ -48194,7 +48239,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="727" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" s="9">
         <v>69420</v>
       </c>
@@ -48220,7 +48265,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="728" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" s="9">
         <v>70154</v>
       </c>
@@ -48245,9 +48290,8 @@
       <c r="H728" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="I728" s="26"/>
-    </row>
-    <row r="729" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="729" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" s="9">
         <v>69757</v>
       </c>
@@ -48272,9 +48316,8 @@
       <c r="H729" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="I729" s="26"/>
-    </row>
-    <row r="730" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="730" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" s="9">
         <v>69391</v>
       </c>
@@ -48299,9 +48342,8 @@
       <c r="H730" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="I730" s="26"/>
-    </row>
-    <row r="731" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="731" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" s="9">
         <v>69769</v>
       </c>
@@ -48326,9 +48368,8 @@
       <c r="H731" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="I731" s="26"/>
-    </row>
-    <row r="732" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="732" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" s="9">
         <v>68888</v>
       </c>
@@ -48353,9 +48394,8 @@
       <c r="H732" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="I732" s="26"/>
-    </row>
-    <row r="733" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="733" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" s="9">
         <v>69369</v>
       </c>
@@ -48380,9 +48420,8 @@
       <c r="H733" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="I733" s="26"/>
-    </row>
-    <row r="734" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="734" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" s="9">
         <v>69762</v>
       </c>
@@ -48407,9 +48446,8 @@
       <c r="H734" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I734" s="26"/>
-    </row>
-    <row r="735" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="735" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" s="9">
         <v>69764</v>
       </c>
@@ -48434,9 +48472,8 @@
       <c r="H735" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="I735" s="26"/>
-    </row>
-    <row r="736" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="736" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" s="9">
         <v>69768</v>
       </c>
@@ -48461,9 +48498,8 @@
       <c r="H736" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="I736" s="26"/>
-    </row>
-    <row r="737" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="737" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" s="9">
         <v>70288</v>
       </c>
@@ -48488,9 +48524,8 @@
       <c r="H737" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I737" s="26"/>
-    </row>
-    <row r="738" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="738" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" s="9">
         <v>69802</v>
       </c>
@@ -48515,9 +48550,8 @@
       <c r="H738" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I738" s="26"/>
-    </row>
-    <row r="739" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="739" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" s="9">
         <v>70153</v>
       </c>
@@ -48542,9 +48576,8 @@
       <c r="H739" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="I739" s="26"/>
-    </row>
-    <row r="740" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="740" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" s="9">
         <v>70157</v>
       </c>
@@ -48569,9 +48602,8 @@
       <c r="H740" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="I740" s="26"/>
-    </row>
-    <row r="741" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="741" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" s="9">
         <v>70197</v>
       </c>
@@ -48596,9 +48628,8 @@
       <c r="H741" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="I741" s="26"/>
-    </row>
-    <row r="742" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="742" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" s="9">
         <v>70160</v>
       </c>
@@ -48623,9 +48654,8 @@
       <c r="H742" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="I742" s="26"/>
-    </row>
-    <row r="743" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="743" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" s="9">
         <v>69811</v>
       </c>
@@ -48650,9 +48680,8 @@
       <c r="H743" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I743" s="26"/>
-    </row>
-    <row r="744" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="744" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" s="9">
         <v>69763</v>
       </c>
@@ -48677,9 +48706,8 @@
       <c r="H744" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="I744" s="26"/>
-    </row>
-    <row r="745" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="745" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" s="9">
         <v>70192</v>
       </c>
@@ -48704,9 +48732,8 @@
       <c r="H745" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I745" s="26"/>
-    </row>
-    <row r="746" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="746" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" s="9">
         <v>69761</v>
       </c>
@@ -48731,9 +48758,8 @@
       <c r="H746" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I746" s="26"/>
-    </row>
-    <row r="747" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="747" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" s="9">
         <v>69814</v>
       </c>
@@ -48758,9 +48784,8 @@
       <c r="H747" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I747" s="26"/>
-    </row>
-    <row r="748" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="748" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" s="9">
         <v>67106</v>
       </c>
@@ -48785,11 +48810,8 @@
       <c r="H748" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="I748" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="749" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="749" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" s="9">
         <v>69852</v>
       </c>
@@ -48805,7 +48827,7 @@
       <c r="E749" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F749" s="27" t="s">
+      <c r="F749" s="26" t="s">
         <v>55</v>
       </c>
       <c r="G749" s="21" t="s">
@@ -48814,11 +48836,8 @@
       <c r="H749" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="I749" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="750" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="750" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" s="9">
         <v>69839</v>
       </c>
@@ -48843,9 +48862,8 @@
       <c r="H750" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I750" s="26"/>
-    </row>
-    <row r="751" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="751" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" s="9">
         <v>70078</v>
       </c>
@@ -48870,9 +48888,8 @@
       <c r="H751" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="I751" s="26"/>
-    </row>
-    <row r="752" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="752" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" s="9">
         <v>70144</v>
       </c>
@@ -48897,9 +48914,8 @@
       <c r="H752" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I752" s="26"/>
-    </row>
-    <row r="753" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="753" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" s="9">
         <v>70152</v>
       </c>
@@ -48924,9 +48940,8 @@
       <c r="H753" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="I753" s="26"/>
-    </row>
-    <row r="754" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="754" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" s="9">
         <v>70158</v>
       </c>
@@ -48951,9 +48966,8 @@
       <c r="H754" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="I754" s="26"/>
-    </row>
-    <row r="755" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="755" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" s="9">
         <v>70203</v>
       </c>
@@ -48978,9 +48992,8 @@
       <c r="H755" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I755" s="26"/>
-    </row>
-    <row r="756" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="756" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" s="9">
         <v>70236</v>
       </c>
@@ -49003,9 +49016,8 @@
         <v>11</v>
       </c>
       <c r="H756" s="16"/>
-      <c r="I756" s="26"/>
-    </row>
-    <row r="757" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="757" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" s="9">
         <v>70235</v>
       </c>
@@ -49028,11 +49040,8 @@
         <v>11</v>
       </c>
       <c r="H757" s="16"/>
-      <c r="I757" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="758" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="758" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" s="9">
         <v>70072</v>
       </c>
@@ -49057,9 +49066,8 @@
       <c r="H758" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="I758" s="26"/>
-    </row>
-    <row r="759" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="759" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" s="9">
         <v>70071</v>
       </c>
@@ -49082,11 +49090,8 @@
         <v>11</v>
       </c>
       <c r="H759" s="16"/>
-      <c r="I759" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="760" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="760" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" s="9">
         <v>70321</v>
       </c>
@@ -49109,9 +49114,8 @@
         <v>11</v>
       </c>
       <c r="H760" s="16"/>
-      <c r="I760" s="26"/>
-    </row>
-    <row r="761" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="761" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" s="9">
         <v>70181</v>
       </c>
@@ -49136,9 +49140,8 @@
       <c r="H761" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="I761" s="26"/>
-    </row>
-    <row r="762" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="762" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" s="9">
         <v>67899</v>
       </c>
@@ -49161,9 +49164,8 @@
         <v>14</v>
       </c>
       <c r="H762" s="16"/>
-      <c r="I762" s="26"/>
-    </row>
-    <row r="763" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="763" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" s="9">
         <v>70319</v>
       </c>
@@ -49188,11 +49190,8 @@
       <c r="H763" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="I763" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="764" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="764" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" s="9">
         <v>69095</v>
       </c>
@@ -49215,9 +49214,8 @@
         <v>11</v>
       </c>
       <c r="H764" s="16"/>
-      <c r="I764" s="26"/>
-    </row>
-    <row r="765" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="765" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" s="9">
         <v>66746</v>
       </c>
@@ -49240,9 +49238,8 @@
         <v>11</v>
       </c>
       <c r="H765" s="16"/>
-      <c r="I765" s="26"/>
-    </row>
-    <row r="766" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="766" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" s="9">
         <v>69094</v>
       </c>
@@ -49265,9 +49262,8 @@
         <v>11</v>
       </c>
       <c r="H766" s="16"/>
-      <c r="I766" s="26"/>
-    </row>
-    <row r="767" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="767" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" s="9">
         <v>70312</v>
       </c>
@@ -49292,11 +49288,8 @@
       <c r="H767" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="I767" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="768" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="768" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" s="9">
         <v>70311</v>
       </c>
@@ -49321,9 +49314,8 @@
       <c r="H768" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I768" s="26"/>
-    </row>
-    <row r="769" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="769" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" s="9">
         <v>70303</v>
       </c>
@@ -49348,9 +49340,8 @@
       <c r="H769" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I769" s="26"/>
-    </row>
-    <row r="770" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="770" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" s="9">
         <v>70298</v>
       </c>
@@ -49373,9 +49364,8 @@
         <v>14</v>
       </c>
       <c r="H770" s="16"/>
-      <c r="I770" s="26"/>
-    </row>
-    <row r="771" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="771" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" s="9">
         <v>70277</v>
       </c>
@@ -49400,11 +49390,8 @@
       <c r="H771" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I771" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="772" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="772" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" s="9">
         <v>70260</v>
       </c>
@@ -49427,11 +49414,8 @@
         <v>14</v>
       </c>
       <c r="H772" s="16"/>
-      <c r="I772" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="773" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="773" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" s="9">
         <v>70255</v>
       </c>
@@ -49454,11 +49438,8 @@
         <v>14</v>
       </c>
       <c r="H773" s="16"/>
-      <c r="I773" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="774" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="774" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" s="9">
         <v>70251</v>
       </c>
@@ -49481,11 +49462,8 @@
         <v>14</v>
       </c>
       <c r="H774" s="16"/>
-      <c r="I774" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="775" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="775" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" s="9">
         <v>69469</v>
       </c>
@@ -49508,11 +49486,8 @@
         <v>11</v>
       </c>
       <c r="H775" s="16"/>
-      <c r="I775" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="776" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="776" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" s="9">
         <v>69470</v>
       </c>
@@ -49535,11 +49510,8 @@
         <v>11</v>
       </c>
       <c r="H776" s="16"/>
-      <c r="I776" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="777" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="777" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" s="9">
         <v>70390</v>
       </c>
@@ -49564,9 +49536,8 @@
       <c r="H777" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I777" s="26"/>
-    </row>
-    <row r="778" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="778" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" s="9">
         <v>69767</v>
       </c>
@@ -49591,9 +49562,8 @@
       <c r="H778" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="I778" s="26"/>
-    </row>
-    <row r="779" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="779" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" s="9">
         <v>70279</v>
       </c>
@@ -49618,9 +49588,8 @@
       <c r="H779" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="I779" s="26"/>
-    </row>
-    <row r="780" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="780" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" s="9">
         <v>70278</v>
       </c>
@@ -49645,9 +49614,8 @@
       <c r="H780" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I780" s="26"/>
-    </row>
-    <row r="781" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="781" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" s="9">
         <v>69803</v>
       </c>
@@ -49672,9 +49640,8 @@
       <c r="H781" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I781" s="26"/>
-    </row>
-    <row r="782" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="782" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" s="9">
         <v>68147</v>
       </c>
@@ -49697,9 +49664,8 @@
         <v>14</v>
       </c>
       <c r="H782" s="16"/>
-      <c r="I782" s="26"/>
-    </row>
-    <row r="783" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="783" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" s="9">
         <v>67824</v>
       </c>
@@ -49722,9 +49688,8 @@
         <v>14</v>
       </c>
       <c r="H783" s="16"/>
-      <c r="I783" s="26"/>
-    </row>
-    <row r="784" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="784" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" s="9">
         <v>69541</v>
       </c>
@@ -49747,9 +49712,8 @@
         <v>14</v>
       </c>
       <c r="H784" s="16"/>
-      <c r="I784" s="26"/>
-    </row>
-    <row r="785" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="785" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" s="9">
         <v>68170</v>
       </c>
@@ -49774,9 +49738,8 @@
       <c r="H785" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="I785" s="26"/>
-    </row>
-    <row r="786" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="786" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" s="9">
         <v>67000</v>
       </c>
@@ -49801,9 +49764,8 @@
       <c r="H786" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="I786" s="26"/>
-    </row>
-    <row r="787" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="787" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" s="9">
         <v>70246</v>
       </c>
@@ -49826,9 +49788,8 @@
         <v>14</v>
       </c>
       <c r="H787" s="16"/>
-      <c r="I787" s="26"/>
-    </row>
-    <row r="788" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="788" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" s="9">
         <v>67939</v>
       </c>
@@ -49851,9 +49812,8 @@
         <v>11</v>
       </c>
       <c r="H788" s="16"/>
-      <c r="I788" s="26"/>
-    </row>
-    <row r="789" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="789" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" s="9">
         <v>69967</v>
       </c>
@@ -49878,9 +49838,8 @@
       <c r="H789" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="I789" s="26"/>
-    </row>
-    <row r="790" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="790" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" s="9">
         <v>70088</v>
       </c>
@@ -49905,9 +49864,8 @@
       <c r="H790" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="I790" s="26"/>
-    </row>
-    <row r="791" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="791" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" s="9">
         <v>69908</v>
       </c>
@@ -49932,9 +49890,8 @@
       <c r="H791" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="I791" s="26"/>
-    </row>
-    <row r="792" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="792" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" s="9">
         <v>69053</v>
       </c>
@@ -49957,9 +49914,8 @@
         <v>11</v>
       </c>
       <c r="H792" s="16"/>
-      <c r="I792" s="26"/>
-    </row>
-    <row r="793" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="793" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" s="9">
         <v>70161</v>
       </c>
@@ -49984,9 +49940,8 @@
       <c r="H793" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="I793" s="26"/>
-    </row>
-    <row r="794" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="794" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" s="9">
         <v>69414</v>
       </c>
@@ -50009,9 +49964,8 @@
         <v>14</v>
       </c>
       <c r="H794" s="16"/>
-      <c r="I794" s="26"/>
-    </row>
-    <row r="795" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="795" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" s="9">
         <v>69448</v>
       </c>
@@ -50034,9 +49988,8 @@
         <v>14</v>
       </c>
       <c r="H795" s="16"/>
-      <c r="I795" s="26"/>
-    </row>
-    <row r="796" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="796" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" s="9">
         <v>70054</v>
       </c>
@@ -50061,9 +50014,8 @@
       <c r="H796" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="I796" s="26"/>
-    </row>
-    <row r="797" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="797" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" s="9">
         <v>69601</v>
       </c>
@@ -50086,9 +50038,8 @@
         <v>14</v>
       </c>
       <c r="H797" s="16"/>
-      <c r="I797" s="26"/>
-    </row>
-    <row r="798" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="798" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" s="9">
         <v>69756</v>
       </c>
@@ -50111,9 +50062,8 @@
         <v>11</v>
       </c>
       <c r="H798" s="16"/>
-      <c r="I798" s="26"/>
-    </row>
-    <row r="799" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="799" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" s="9">
         <v>70156</v>
       </c>
@@ -50136,10 +50086,9 @@
         <v>14</v>
       </c>
       <c r="H799" s="16"/>
-      <c r="I799" s="26"/>
-    </row>
-    <row r="800" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A800" s="28">
+    </row>
+    <row r="800" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A800" s="27">
         <v>69368</v>
       </c>
       <c r="B800" s="17" t="s">
@@ -50161,9 +50110,8 @@
         <v>11</v>
       </c>
       <c r="H800" s="16"/>
-      <c r="I800" s="26"/>
-    </row>
-    <row r="801" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="801" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" s="9">
         <v>69050</v>
       </c>
@@ -50186,9 +50134,8 @@
         <v>11</v>
       </c>
       <c r="H801" s="16"/>
-      <c r="I801" s="26"/>
-    </row>
-    <row r="802" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="802" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" s="9">
         <v>66227</v>
       </c>
@@ -50211,9 +50158,8 @@
         <v>11</v>
       </c>
       <c r="H802" s="16"/>
-      <c r="I802" s="26"/>
-    </row>
-    <row r="803" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="803" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" s="9">
         <v>69959</v>
       </c>
@@ -50238,9 +50184,8 @@
       <c r="H803" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="I803" s="26"/>
-    </row>
-    <row r="804" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="804" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" s="9">
         <v>70209</v>
       </c>
@@ -50265,9 +50210,8 @@
       <c r="H804" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="I804" s="26"/>
-    </row>
-    <row r="805" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="805" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" s="9">
         <v>70225</v>
       </c>
@@ -50292,10 +50236,9 @@
       <c r="H805" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="I805" s="26"/>
-    </row>
-    <row r="806" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A806" s="28">
+    </row>
+    <row r="806" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A806" s="27">
         <v>69754</v>
       </c>
       <c r="B806" s="17" t="s">
@@ -50319,9 +50262,8 @@
       <c r="H806" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="I806" s="26"/>
-    </row>
-    <row r="807" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="807" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" s="9">
         <v>66980</v>
       </c>
@@ -50344,9 +50286,8 @@
         <v>11</v>
       </c>
       <c r="H807" s="16"/>
-      <c r="I807" s="26"/>
-    </row>
-    <row r="808" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="808" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" s="9">
         <v>69185</v>
       </c>
@@ -50369,9 +50310,8 @@
         <v>11</v>
       </c>
       <c r="H808" s="16"/>
-      <c r="I808" s="26"/>
-    </row>
-    <row r="809" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="809" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" s="9">
         <v>70365</v>
       </c>
@@ -50396,9 +50336,8 @@
       <c r="H809" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I809" s="26"/>
-    </row>
-    <row r="810" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="810" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" s="9">
         <v>70366</v>
       </c>
@@ -50423,9 +50362,8 @@
       <c r="H810" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I810" s="26"/>
-    </row>
-    <row r="811" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="811" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" s="9">
         <v>70368</v>
       </c>
@@ -50450,9 +50388,8 @@
       <c r="H811" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I811" s="26"/>
-    </row>
-    <row r="812" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="812" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" s="9">
         <v>70370</v>
       </c>
@@ -50477,9 +50414,8 @@
       <c r="H812" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I812" s="26"/>
-    </row>
-    <row r="813" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="813" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" s="9">
         <v>70374</v>
       </c>
@@ -50504,9 +50440,8 @@
       <c r="H813" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I813" s="26"/>
-    </row>
-    <row r="814" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="814" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" s="9">
         <v>70372</v>
       </c>
@@ -50531,9 +50466,8 @@
       <c r="H814" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I814" s="26"/>
-    </row>
-    <row r="815" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="815" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" s="9">
         <v>70378</v>
       </c>
@@ -50558,9 +50492,8 @@
       <c r="H815" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I815" s="26"/>
-    </row>
-    <row r="816" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="816" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" s="9">
         <v>70375</v>
       </c>
@@ -50585,9 +50518,8 @@
       <c r="H816" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I816" s="26"/>
-    </row>
-    <row r="817" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="817" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" s="9">
         <v>70373</v>
       </c>
@@ -50612,9 +50544,8 @@
       <c r="H817" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I817" s="26"/>
-    </row>
-    <row r="818" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="818" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" s="9">
         <v>68822</v>
       </c>
@@ -50639,9 +50570,8 @@
       <c r="H818" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="I818" s="26"/>
-    </row>
-    <row r="819" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="819" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" s="9">
         <v>69687</v>
       </c>
@@ -50666,9 +50596,8 @@
       <c r="H819" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="I819" s="26"/>
-    </row>
-    <row r="820" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="820" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" s="9">
         <v>70241</v>
       </c>
@@ -50693,9 +50622,8 @@
       <c r="H820" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="I820" s="26"/>
-    </row>
-    <row r="821" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="821" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" s="9">
         <v>70314</v>
       </c>
@@ -50720,9 +50648,8 @@
       <c r="H821" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="I821" s="26"/>
-    </row>
-    <row r="822" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="822" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" s="9">
         <v>70098</v>
       </c>
@@ -50747,9 +50674,8 @@
       <c r="H822" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I822" s="26"/>
-    </row>
-    <row r="823" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="823" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" s="9">
         <v>70097</v>
       </c>
@@ -50774,9 +50700,8 @@
       <c r="H823" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I823" s="26"/>
-    </row>
-    <row r="824" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="824" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" s="9">
         <v>70095</v>
       </c>
@@ -50801,9 +50726,8 @@
       <c r="H824" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I824" s="26"/>
-    </row>
-    <row r="825" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="825" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" s="9">
         <v>70139</v>
       </c>
@@ -50826,9 +50750,8 @@
         <v>14</v>
       </c>
       <c r="H825" s="16"/>
-      <c r="I825" s="26"/>
-    </row>
-    <row r="826" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="826" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" s="9">
         <v>70126</v>
       </c>
@@ -50853,9 +50776,8 @@
       <c r="H826" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I826" s="26"/>
-    </row>
-    <row r="827" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="827" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" s="9">
         <v>70124</v>
       </c>
@@ -50880,9 +50802,8 @@
       <c r="H827" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I827" s="26"/>
-    </row>
-    <row r="828" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="828" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" s="9">
         <v>70117</v>
       </c>
@@ -50907,9 +50828,8 @@
       <c r="H828" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I828" s="26"/>
-    </row>
-    <row r="829" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="829" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" s="9">
         <v>70108</v>
       </c>
@@ -50934,9 +50854,8 @@
       <c r="H829" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I829" s="26"/>
-    </row>
-    <row r="830" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="830" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" s="9">
         <v>70101</v>
       </c>
@@ -50961,9 +50880,8 @@
       <c r="H830" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I830" s="26"/>
-    </row>
-    <row r="831" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="831" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" s="9">
         <v>70100</v>
       </c>
@@ -50988,9 +50906,8 @@
       <c r="H831" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I831" s="26"/>
-    </row>
-    <row r="832" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="832" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" s="9">
         <v>70143</v>
       </c>
@@ -51013,9 +50930,8 @@
         <v>14</v>
       </c>
       <c r="H832" s="16"/>
-      <c r="I832" s="26"/>
-    </row>
-    <row r="833" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="833" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" s="9">
         <v>70173</v>
       </c>
@@ -51038,9 +50954,8 @@
         <v>14</v>
       </c>
       <c r="H833" s="16"/>
-      <c r="I833" s="26"/>
-    </row>
-    <row r="834" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="834" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" s="9">
         <v>70224</v>
       </c>
@@ -51063,9 +50978,8 @@
         <v>14</v>
       </c>
       <c r="H834" s="16"/>
-      <c r="I834" s="26"/>
-    </row>
-    <row r="835" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="835" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" s="9">
         <v>70222</v>
       </c>
@@ -51088,9 +51002,8 @@
         <v>14</v>
       </c>
       <c r="H835" s="16"/>
-      <c r="I835" s="26"/>
-    </row>
-    <row r="836" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="836" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="9">
         <v>70217</v>
       </c>
@@ -51113,9 +51026,8 @@
         <v>14</v>
       </c>
       <c r="H836" s="16"/>
-      <c r="I836" s="26"/>
-    </row>
-    <row r="837" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="837" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" s="9">
         <v>70190</v>
       </c>
@@ -51138,9 +51050,8 @@
         <v>14</v>
       </c>
       <c r="H837" s="16"/>
-      <c r="I837" s="26"/>
-    </row>
-    <row r="838" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="838" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" s="9">
         <v>70179</v>
       </c>
@@ -51163,9 +51074,8 @@
         <v>14</v>
       </c>
       <c r="H838" s="16"/>
-      <c r="I838" s="26"/>
-    </row>
-    <row r="839" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="839" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" s="9">
         <v>70304</v>
       </c>
@@ -51190,9 +51100,8 @@
       <c r="H839" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I839" s="26"/>
-    </row>
-    <row r="840" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="840" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" s="9">
         <v>70302</v>
       </c>
@@ -51215,9 +51124,8 @@
         <v>14</v>
       </c>
       <c r="H840" s="16"/>
-      <c r="I840" s="26"/>
-    </row>
-    <row r="841" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="841" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" s="9">
         <v>70301</v>
       </c>
@@ -51240,9 +51148,8 @@
         <v>14</v>
       </c>
       <c r="H841" s="16"/>
-      <c r="I841" s="26"/>
-    </row>
-    <row r="842" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="842" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="9">
         <v>70293</v>
       </c>
@@ -51265,9 +51172,8 @@
         <v>14</v>
       </c>
       <c r="H842" s="16"/>
-      <c r="I842" s="26"/>
-    </row>
-    <row r="843" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="843" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" s="9">
         <v>70292</v>
       </c>
@@ -51290,9 +51196,8 @@
         <v>14</v>
       </c>
       <c r="H843" s="16"/>
-      <c r="I843" s="26"/>
-    </row>
-    <row r="844" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="844" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="9">
         <v>70291</v>
       </c>
@@ -51315,9 +51220,8 @@
         <v>14</v>
       </c>
       <c r="H844" s="16"/>
-      <c r="I844" s="26"/>
-    </row>
-    <row r="845" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="845" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" s="9">
         <v>70290</v>
       </c>
@@ -51340,9 +51244,8 @@
         <v>14</v>
       </c>
       <c r="H845" s="16"/>
-      <c r="I845" s="26"/>
-    </row>
-    <row r="846" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="846" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" s="9">
         <v>70287</v>
       </c>
@@ -51365,9 +51268,8 @@
         <v>14</v>
       </c>
       <c r="H846" s="16"/>
-      <c r="I846" s="26"/>
-    </row>
-    <row r="847" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="847" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" s="9">
         <v>70284</v>
       </c>
@@ -51390,9 +51292,8 @@
         <v>14</v>
       </c>
       <c r="H847" s="16"/>
-      <c r="I847" s="26"/>
-    </row>
-    <row r="848" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="848" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" s="9">
         <v>70282</v>
       </c>
@@ -51415,9 +51316,8 @@
         <v>14</v>
       </c>
       <c r="H848" s="16"/>
-      <c r="I848" s="26"/>
-    </row>
-    <row r="849" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="849" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" s="9">
         <v>70052</v>
       </c>
@@ -51440,9 +51340,8 @@
         <v>14</v>
       </c>
       <c r="H849" s="16"/>
-      <c r="I849" s="26"/>
-    </row>
-    <row r="850" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="850" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" s="9">
         <v>69891</v>
       </c>
@@ -51465,9 +51364,8 @@
         <v>14</v>
       </c>
       <c r="H850" s="16"/>
-      <c r="I850" s="26"/>
-    </row>
-    <row r="851" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="851" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" s="9">
         <v>70388</v>
       </c>
@@ -51490,9 +51388,8 @@
         <v>14</v>
       </c>
       <c r="H851" s="16"/>
-      <c r="I851" s="26"/>
-    </row>
-    <row r="852" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="852" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" s="9">
         <v>70453</v>
       </c>
@@ -51515,9 +51412,8 @@
         <v>14</v>
       </c>
       <c r="H852" s="16"/>
-      <c r="I852" s="26"/>
-    </row>
-    <row r="853" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="853" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" s="9">
         <v>70226</v>
       </c>
@@ -51540,9 +51436,8 @@
         <v>14</v>
       </c>
       <c r="H853" s="16"/>
-      <c r="I853" s="26"/>
-    </row>
-    <row r="854" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="854" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" s="9">
         <v>70457</v>
       </c>
@@ -51565,9 +51460,8 @@
         <v>14</v>
       </c>
       <c r="H854" s="16"/>
-      <c r="I854" s="26"/>
-    </row>
-    <row r="855" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="855" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" s="9">
         <v>70456</v>
       </c>
@@ -51590,9 +51484,8 @@
         <v>14</v>
       </c>
       <c r="H855" s="16"/>
-      <c r="I855" s="26"/>
-    </row>
-    <row r="856" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="856" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" s="9">
         <v>68923</v>
       </c>
@@ -51615,9 +51508,8 @@
         <v>14</v>
       </c>
       <c r="H856" s="16"/>
-      <c r="I856" s="26"/>
-    </row>
-    <row r="857" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="857" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" s="9">
         <v>68793</v>
       </c>
@@ -51640,9 +51532,8 @@
         <v>14</v>
       </c>
       <c r="H857" s="16"/>
-      <c r="I857" s="26"/>
-    </row>
-    <row r="858" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="858" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" s="9">
         <v>68470</v>
       </c>
@@ -51665,9 +51556,8 @@
         <v>14</v>
       </c>
       <c r="H858" s="16"/>
-      <c r="I858" s="26"/>
-    </row>
-    <row r="859" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="859" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" s="9">
         <v>70315</v>
       </c>
@@ -51692,9 +51582,8 @@
       <c r="H859" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="I859" s="26"/>
-    </row>
-    <row r="860" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="860" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" s="9">
         <v>70367</v>
       </c>
@@ -51719,9 +51608,8 @@
       <c r="H860" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I860" s="26"/>
-    </row>
-    <row r="861" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="861" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="9">
         <v>70369</v>
       </c>
@@ -51746,9 +51634,8 @@
       <c r="H861" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I861" s="26"/>
-    </row>
-    <row r="862" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="862" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="9">
         <v>70381</v>
       </c>
@@ -51773,9 +51660,8 @@
       <c r="H862" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I862" s="26"/>
-    </row>
-    <row r="863" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="863" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" s="9">
         <v>70371</v>
       </c>
@@ -51800,9 +51686,8 @@
       <c r="H863" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="I863" s="26"/>
-    </row>
-    <row r="864" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="864" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" s="9">
         <v>70380</v>
       </c>
@@ -51827,9 +51712,8 @@
       <c r="H864" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I864" s="26"/>
-    </row>
-    <row r="865" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="865" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" s="9">
         <v>70239</v>
       </c>
@@ -51854,9 +51738,8 @@
       <c r="H865" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="I865" s="26"/>
-    </row>
-    <row r="866" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="866" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" s="9">
         <v>70090</v>
       </c>
@@ -51881,9 +51764,8 @@
       <c r="H866" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="I866" s="26"/>
-    </row>
-    <row r="867" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="867" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" s="9">
         <v>70276</v>
       </c>
@@ -51908,9 +51790,8 @@
       <c r="H867" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I867" s="26"/>
-    </row>
-    <row r="868" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="868" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" s="9">
         <v>70274</v>
       </c>
@@ -51935,9 +51816,8 @@
       <c r="H868" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I868" s="26"/>
-    </row>
-    <row r="869" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="869" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" s="9">
         <v>70273</v>
       </c>
@@ -51962,9 +51842,8 @@
       <c r="H869" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I869" s="26"/>
-    </row>
-    <row r="870" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="870" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" s="9">
         <v>70271</v>
       </c>
@@ -51989,9 +51868,8 @@
       <c r="H870" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="I870" s="26"/>
-    </row>
-    <row r="871" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="871" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" s="9">
         <v>70268</v>
       </c>
@@ -52016,9 +51894,8 @@
       <c r="H871" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I871" s="26"/>
-    </row>
-    <row r="872" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="872" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" s="9">
         <v>70230</v>
       </c>
@@ -52043,9 +51920,8 @@
       <c r="H872" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I872" s="26"/>
-    </row>
-    <row r="873" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="873" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" s="9">
         <v>70320</v>
       </c>
@@ -52070,9 +51946,8 @@
       <c r="H873" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="I873" s="26"/>
-    </row>
-    <row r="874" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="874" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" s="9">
         <v>69389</v>
       </c>
@@ -52097,17 +51972,20 @@
       <c r="H874" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="I874" s="26"/>
-    </row>
-    <row r="875" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A875" s="9"/>
+    </row>
+    <row r="875" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A875" s="27">
+        <v>69704</v>
+      </c>
       <c r="B875" s="17" t="s">
         <v>34</v>
       </c>
       <c r="C875" s="18">
         <v>46315</v>
       </c>
-      <c r="D875" s="12"/>
+      <c r="D875" s="12">
+        <v>1</v>
+      </c>
       <c r="E875" s="13" t="s">
         <v>9</v>
       </c>
@@ -52116,6 +51994,1497 @@
       </c>
       <c r="G875" s="20" t="s">
         <v>14</v>
+      </c>
+      <c r="H875" s="16"/>
+    </row>
+    <row r="876" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A876" s="9">
+        <v>69860</v>
+      </c>
+      <c r="B876" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C876" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D876" s="12">
+        <v>1</v>
+      </c>
+      <c r="E876" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F876" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G876" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H876" s="16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="877" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A877" s="9">
+        <v>68823</v>
+      </c>
+      <c r="B877" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C877" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D877" s="12">
+        <v>1</v>
+      </c>
+      <c r="E877" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F877" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G877" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H877" s="16"/>
+    </row>
+    <row r="878" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A878" s="9">
+        <v>70317</v>
+      </c>
+      <c r="B878" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C878" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D878" s="12">
+        <v>1</v>
+      </c>
+      <c r="E878" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F878" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G878" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H878" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="879" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A879" s="27">
+        <v>69571</v>
+      </c>
+      <c r="B879" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C879" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D879" s="12">
+        <v>1</v>
+      </c>
+      <c r="E879" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F879" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G879" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H879" s="16"/>
+    </row>
+    <row r="880" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A880" s="27">
+        <v>69738</v>
+      </c>
+      <c r="B880" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C880" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D880" s="12">
+        <v>5</v>
+      </c>
+      <c r="E880" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F880" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G880" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H880" s="16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="881" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A881" s="9">
+        <v>69349</v>
+      </c>
+      <c r="B881" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C881" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D881" s="12">
+        <v>4</v>
+      </c>
+      <c r="E881" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F881" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G881" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H881" s="16"/>
+    </row>
+    <row r="882" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A882" s="9">
+        <v>70234</v>
+      </c>
+      <c r="B882" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C882" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D882" s="12">
+        <v>9</v>
+      </c>
+      <c r="E882" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F882" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G882" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H882" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="883" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A883" s="9">
+        <v>69298</v>
+      </c>
+      <c r="B883" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C883" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D883" s="12">
+        <v>10</v>
+      </c>
+      <c r="E883" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F883" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G883" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H883" s="16"/>
+    </row>
+    <row r="884" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A884" s="9">
+        <v>70452</v>
+      </c>
+      <c r="B884" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C884" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D884" s="12">
+        <v>2</v>
+      </c>
+      <c r="E884" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F884" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G884" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H884" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="885" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A885" s="9">
+        <v>70464</v>
+      </c>
+      <c r="B885" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C885" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D885" s="12">
+        <v>1</v>
+      </c>
+      <c r="E885" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F885" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G885" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H885" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="886" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A886" s="9">
+        <v>70309</v>
+      </c>
+      <c r="B886" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C886" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D886" s="12">
+        <v>0</v>
+      </c>
+      <c r="E886" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F886" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G886" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H886" s="16"/>
+    </row>
+    <row r="887" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A887" s="9">
+        <v>70364</v>
+      </c>
+      <c r="B887" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C887" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D887" s="12">
+        <v>4</v>
+      </c>
+      <c r="E887" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F887" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G887" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H887" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="888" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A888" s="9">
+        <v>70447</v>
+      </c>
+      <c r="B888" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C888" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D888" s="12">
+        <v>2</v>
+      </c>
+      <c r="E888" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F888" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G888" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H888" s="16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="889" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A889" s="9">
+        <v>70391</v>
+      </c>
+      <c r="B889" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C889" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D889" s="12">
+        <v>1</v>
+      </c>
+      <c r="E889" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F889" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G889" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H889" s="16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="890" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A890" s="9">
+        <v>70389</v>
+      </c>
+      <c r="B890" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C890" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D890" s="12">
+        <v>0</v>
+      </c>
+      <c r="E890" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F890" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G890" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H890" s="16"/>
+    </row>
+    <row r="891" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A891" s="9">
+        <v>70386</v>
+      </c>
+      <c r="B891" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C891" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D891" s="12">
+        <v>0</v>
+      </c>
+      <c r="E891" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F891" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G891" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H891" s="16"/>
+    </row>
+    <row r="892" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A892" s="9">
+        <v>70280</v>
+      </c>
+      <c r="B892" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C892" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D892" s="12">
+        <v>3</v>
+      </c>
+      <c r="E892" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F892" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G892" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H892" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="893" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A893" s="9">
+        <v>70384</v>
+      </c>
+      <c r="B893" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C893" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D893" s="12">
+        <v>4</v>
+      </c>
+      <c r="E893" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F893" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G893" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H893" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="894" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A894" s="9">
+        <v>70306</v>
+      </c>
+      <c r="B894" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C894" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D894" s="12">
+        <v>4</v>
+      </c>
+      <c r="E894" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F894" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G894" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H894" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="895" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A895" s="9">
+        <v>70281</v>
+      </c>
+      <c r="B895" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C895" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D895" s="12">
+        <v>4</v>
+      </c>
+      <c r="E895" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F895" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G895" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H895" s="16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="896" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A896" s="9">
+        <v>69980</v>
+      </c>
+      <c r="B896" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C896" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D896" s="12">
+        <v>2</v>
+      </c>
+      <c r="E896" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F896" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G896" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H896" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="897" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A897" s="9">
+        <v>70151</v>
+      </c>
+      <c r="B897" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C897" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D897" s="12">
+        <v>3</v>
+      </c>
+      <c r="E897" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F897" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G897" s="28"/>
+      <c r="H897" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="898" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A898" s="9">
+        <v>70185</v>
+      </c>
+      <c r="B898" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C898" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D898" s="12">
+        <v>13</v>
+      </c>
+      <c r="E898" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F898" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G898" s="28"/>
+      <c r="H898" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="899" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A899" s="9">
+        <v>69838</v>
+      </c>
+      <c r="B899" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C899" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D899" s="12">
+        <v>0</v>
+      </c>
+      <c r="E899" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F899" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G899" s="28"/>
+      <c r="H899" s="16"/>
+    </row>
+    <row r="900" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A900" s="9">
+        <v>69823</v>
+      </c>
+      <c r="B900" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C900" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D900" s="12">
+        <v>0</v>
+      </c>
+      <c r="E900" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F900" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G900" s="28"/>
+      <c r="H900" s="16"/>
+    </row>
+    <row r="901" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A901" s="9">
+        <v>70259</v>
+      </c>
+      <c r="B901" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C901" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D901" s="12">
+        <v>1</v>
+      </c>
+      <c r="E901" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F901" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G901" s="28"/>
+      <c r="H901" s="16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="902" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A902" s="9">
+        <v>70261</v>
+      </c>
+      <c r="B902" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C902" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D902" s="12">
+        <v>3</v>
+      </c>
+      <c r="E902" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F902" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G902" s="28"/>
+      <c r="H902" s="16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="903" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A903" s="9">
+        <v>69816</v>
+      </c>
+      <c r="B903" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C903" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D903" s="12">
+        <v>4</v>
+      </c>
+      <c r="E903" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F903" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G903" s="28"/>
+      <c r="H903" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="904" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A904" s="9">
+        <v>70377</v>
+      </c>
+      <c r="B904" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C904" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D904" s="12">
+        <v>0</v>
+      </c>
+      <c r="E904" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F904" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G904" s="28"/>
+      <c r="H904" s="16"/>
+    </row>
+    <row r="905" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A905" s="9">
+        <v>68224</v>
+      </c>
+      <c r="B905" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C905" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D905" s="12">
+        <v>0</v>
+      </c>
+      <c r="E905" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F905" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G905" s="28"/>
+      <c r="H905" s="16"/>
+    </row>
+    <row r="906" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A906" s="9">
+        <v>70229</v>
+      </c>
+      <c r="B906" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C906" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D906" s="12">
+        <v>2</v>
+      </c>
+      <c r="E906" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F906" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G906" s="28"/>
+      <c r="H906" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="907" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A907" s="9">
+        <v>68361</v>
+      </c>
+      <c r="B907" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C907" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D907" s="12">
+        <v>0</v>
+      </c>
+      <c r="E907" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F907" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G907" s="28"/>
+      <c r="H907" s="16"/>
+    </row>
+    <row r="908" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A908" s="9">
+        <v>70188</v>
+      </c>
+      <c r="B908" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C908" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D908" s="12">
+        <v>1</v>
+      </c>
+      <c r="E908" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F908" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G908" s="28"/>
+      <c r="H908" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="909" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A909" s="9">
+        <v>69893</v>
+      </c>
+      <c r="B909" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C909" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D909" s="12">
+        <v>3</v>
+      </c>
+      <c r="E909" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F909" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G909" s="28"/>
+      <c r="H909" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="910" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A910" s="9">
+        <v>70220</v>
+      </c>
+      <c r="B910" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C910" s="18">
+        <v>46315</v>
+      </c>
+      <c r="D910" s="12">
+        <v>0</v>
+      </c>
+      <c r="E910" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F910" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G910" s="28"/>
+      <c r="H910" s="16"/>
+    </row>
+    <row r="911" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A911" s="9">
+        <v>70182</v>
+      </c>
+      <c r="B911" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C911" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D911" s="12">
+        <v>14</v>
+      </c>
+      <c r="E911" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F911" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G911" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H911" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="912" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A912" s="9">
+        <v>70186</v>
+      </c>
+      <c r="B912" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C912" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D912" s="12">
+        <v>5</v>
+      </c>
+      <c r="E912" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F912" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G912" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H912" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="913" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A913" s="9">
+        <v>68654</v>
+      </c>
+      <c r="B913" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C913" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D913" s="12">
+        <v>0</v>
+      </c>
+      <c r="E913" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F913" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G913" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H913" s="16"/>
+    </row>
+    <row r="914" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A914" s="9">
+        <v>68642</v>
+      </c>
+      <c r="B914" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C914" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D914" s="12">
+        <v>0</v>
+      </c>
+      <c r="E914" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F914" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G914" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H914" s="16"/>
+    </row>
+    <row r="915" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A915" s="9">
+        <v>70233</v>
+      </c>
+      <c r="B915" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C915" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D915" s="12">
+        <v>1</v>
+      </c>
+      <c r="E915" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F915" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G915" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H915" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="916" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A916" s="9">
+        <v>70232</v>
+      </c>
+      <c r="B916" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C916" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D916" s="12">
+        <v>2</v>
+      </c>
+      <c r="E916" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F916" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G916" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H916" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="917" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A917" s="27">
+        <v>69388</v>
+      </c>
+      <c r="B917" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C917" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D917" s="12">
+        <v>6</v>
+      </c>
+      <c r="E917" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F917" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G917" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H917" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="918" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A918" s="27">
+        <v>69798</v>
+      </c>
+      <c r="B918" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C918" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D918" s="12">
+        <v>9</v>
+      </c>
+      <c r="E918" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F918" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G918" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H918" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="919" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A919" s="9">
+        <v>69799</v>
+      </c>
+      <c r="B919" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C919" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D919" s="12">
+        <v>2</v>
+      </c>
+      <c r="E919" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F919" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G919" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H919" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="920" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A920" s="9">
+        <v>69819</v>
+      </c>
+      <c r="B920" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C920" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D920" s="12">
+        <v>14</v>
+      </c>
+      <c r="E920" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F920" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G920" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H920" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="921" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A921" s="9">
+        <v>69817</v>
+      </c>
+      <c r="B921" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C921" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D921" s="12">
+        <v>10</v>
+      </c>
+      <c r="E921" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F921" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G921" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H921" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="922" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A922" s="9">
+        <v>70180</v>
+      </c>
+      <c r="B922" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C922" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D922" s="12">
+        <v>21</v>
+      </c>
+      <c r="E922" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F922" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G922" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H922" s="16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="923" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A923" s="27">
+        <v>70312</v>
+      </c>
+      <c r="B923" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C923" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D923" s="12">
+        <v>16</v>
+      </c>
+      <c r="E923" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F923" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G923" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H923" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="924" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A924" s="27">
+        <v>69930</v>
+      </c>
+      <c r="B924" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C924" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D924" s="12">
+        <v>1</v>
+      </c>
+      <c r="E924" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F924" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G924" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H924" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="925" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A925" s="9">
+        <v>69418</v>
+      </c>
+      <c r="B925" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C925" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D925" s="12">
+        <v>0</v>
+      </c>
+      <c r="E925" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F925" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G925" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H925" s="16"/>
+    </row>
+    <row r="926" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A926" s="9">
+        <v>68156</v>
+      </c>
+      <c r="B926" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C926" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D926" s="12">
+        <v>0</v>
+      </c>
+      <c r="E926" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F926" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G926" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H926" s="16"/>
+    </row>
+    <row r="927" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A927" s="9">
+        <v>66413</v>
+      </c>
+      <c r="B927" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C927" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D927" s="12">
+        <v>0</v>
+      </c>
+      <c r="E927" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F927" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G927" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H927" s="16"/>
+    </row>
+    <row r="928" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A928" s="9">
+        <v>66252</v>
+      </c>
+      <c r="B928" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C928" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D928" s="12">
+        <v>0</v>
+      </c>
+      <c r="E928" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F928" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G928" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H928" s="16"/>
+    </row>
+    <row r="929" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A929" s="9">
+        <v>69237</v>
+      </c>
+      <c r="B929" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C929" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D929" s="12">
+        <v>0</v>
+      </c>
+      <c r="E929" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F929" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G929" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H929" s="16"/>
+    </row>
+    <row r="930" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A930" s="9">
+        <v>70147</v>
+      </c>
+      <c r="B930" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C930" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D930" s="12">
+        <v>13</v>
+      </c>
+      <c r="E930" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F930" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G930" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H930" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="931" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A931" s="9">
+        <v>67001</v>
+      </c>
+      <c r="B931" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C931" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D931" s="12">
+        <v>1</v>
+      </c>
+      <c r="E931" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F931" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G931" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H931" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="932" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A932" s="9">
+        <v>69520</v>
+      </c>
+      <c r="B932" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C932" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D932" s="12">
+        <v>0</v>
+      </c>
+      <c r="E932" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F932" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G932" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H932" s="16"/>
+    </row>
+    <row r="933" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A933" s="27">
+        <v>70230</v>
+      </c>
+      <c r="B933" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C933" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D933" s="12">
+        <v>4</v>
+      </c>
+      <c r="E933" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F933" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G933" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H933" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="934" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A934" s="9">
+        <v>70237</v>
+      </c>
+      <c r="B934" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C934" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D934" s="12">
+        <v>1</v>
+      </c>
+      <c r="E934" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F934" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G934" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H934" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="935" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A935" s="9">
+        <v>70017</v>
+      </c>
+      <c r="B935" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C935" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D935" s="12">
+        <v>12</v>
+      </c>
+      <c r="E935" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F935" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G935" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H935" s="16" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -52174,7 +53543,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="str" cm="1">
-        <f t="array" ref="A1:A14">_xlfn.UNIQUE(DadosBrutos!C1:C875)</f>
+        <f t="array" ref="A1:A15">_xlfn.UNIQUE(DadosBrutos!C1:C935)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="23" t="s">
@@ -52295,11 +53664,17 @@
       </c>
       <c r="B14" s="22">
         <f>COUNTIF(DadosBrutos!C:C, A14)</f>
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
+      <c r="A15" s="24">
+        <v>46316</v>
+      </c>
+      <c r="B15" s="22">
+        <f>COUNTIF(DadosBrutos!C:C, A15)</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
@@ -54455,7 +55830,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="str" cm="1">
-        <f t="array" ref="A1:A14">_xlfn.UNIQUE(DadosBrutos!C1:C875)</f>
+        <f t="array" ref="A1:A15">_xlfn.UNIQUE(DadosBrutos!C1:C935)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="23" t="s">
@@ -54627,15 +56002,25 @@
       </c>
       <c r="B14">
         <f>COUNTIFS(DadosBrutos!C:C, A14, DadosBrutos!G:G, "SAUDAVEL")</f>
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C14">
         <f>COUNTIFS(DadosBrutos!C:C, A14, DadosBrutos!G:G, "BACKLOG")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
+      <c r="A15" s="24">
+        <v>46316</v>
+      </c>
+      <c r="B15">
+        <f>COUNTIFS(DadosBrutos!C:C, A15, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <f>COUNTIFS(DadosBrutos!C:C, A15, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>

--- a/DadosProducao.xlsx
+++ b/DadosProducao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B88C92-47BB-4EF9-8034-4D8BFA9F9CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A978BDAA-FAB8-4C4E-8523-6C8962F8B57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
   </bookViews>
   <sheets>
     <sheet name="DadosBrutos" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4291" uniqueCount="167">
   <si>
     <t>PV</t>
   </si>
@@ -547,6 +547,45 @@
   <si>
     <t>SECONCI HELIOPOLIS</t>
   </si>
+  <si>
+    <t>TECNOLAB UNID XIII</t>
+  </si>
+  <si>
+    <t>TECNOLAB UNIDADE XII</t>
+  </si>
+  <si>
+    <t>TECNOLAB UNIDADE VII</t>
+  </si>
+  <si>
+    <t>TECNOLAB</t>
+  </si>
+  <si>
+    <t>HOSPITAL MORIAH 19.0</t>
+  </si>
+  <si>
+    <t>VITOR HUGO</t>
+  </si>
+  <si>
+    <t>OSWALDO CRUZ SP</t>
+  </si>
+  <si>
+    <t>PEDRO H.</t>
+  </si>
+  <si>
+    <t>CSSM</t>
+  </si>
+  <si>
+    <t>DASA 45.796.554/0018</t>
+  </si>
+  <si>
+    <t>DASA HOSP BRASILIA</t>
+  </si>
+  <si>
+    <t>SECONCI ITAPECERICA</t>
+  </si>
+  <si>
+    <t>NATHALIE</t>
+  </si>
 </sst>
 </file>
 
@@ -670,7 +709,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,6 +755,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF2D0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -849,7 +900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -899,6 +950,8 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28168,7 +28221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B0C76F-2D49-44D6-9EF1-05536D6E01AD}">
-  <dimension ref="A1:H935"/>
+  <dimension ref="A1:H1008"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -53486,6 +53539,1844 @@
       <c r="H935" s="16" t="s">
         <v>137</v>
       </c>
+    </row>
+    <row r="936" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A936" s="9">
+        <v>70249</v>
+      </c>
+      <c r="B936" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C936" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D936" s="12">
+        <v>6</v>
+      </c>
+      <c r="E936" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F936" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G936" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H936" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="937" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A937" s="9">
+        <v>70488</v>
+      </c>
+      <c r="B937" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C937" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D937" s="12">
+        <v>2</v>
+      </c>
+      <c r="E937" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F937" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G937" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H937" s="16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="938" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A938" s="9">
+        <v>70487</v>
+      </c>
+      <c r="B938" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C938" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D938" s="12">
+        <v>4</v>
+      </c>
+      <c r="E938" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F938" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G938" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H938" s="16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="939" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A939" s="9">
+        <v>70467</v>
+      </c>
+      <c r="B939" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C939" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D939" s="12">
+        <v>2</v>
+      </c>
+      <c r="E939" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F939" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G939" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H939" s="16"/>
+    </row>
+    <row r="940" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A940" s="9">
+        <v>70480</v>
+      </c>
+      <c r="B940" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C940" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D940" s="12">
+        <v>4</v>
+      </c>
+      <c r="E940" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F940" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G940" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H940" s="16"/>
+    </row>
+    <row r="941" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A941" s="9">
+        <v>70479</v>
+      </c>
+      <c r="B941" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C941" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D941" s="12">
+        <v>3</v>
+      </c>
+      <c r="E941" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F941" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G941" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H941" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="942" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A942" s="9">
+        <v>70466</v>
+      </c>
+      <c r="B942" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C942" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D942" s="12">
+        <v>4</v>
+      </c>
+      <c r="E942" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F942" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G942" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H942" s="16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="943" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A943" s="9">
+        <v>70462</v>
+      </c>
+      <c r="B943" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C943" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D943" s="12">
+        <v>1</v>
+      </c>
+      <c r="E943" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F943" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G943" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H943" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="944" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A944" s="9">
+        <v>70118</v>
+      </c>
+      <c r="B944" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C944" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D944" s="12">
+        <v>1</v>
+      </c>
+      <c r="E944" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F944" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G944" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H944" s="16"/>
+    </row>
+    <row r="945" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A945" s="9">
+        <v>69521</v>
+      </c>
+      <c r="B945" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C945" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D945" s="12">
+        <v>1</v>
+      </c>
+      <c r="E945" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F945" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G945" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H945" s="16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="946" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A946" s="9">
+        <v>68248</v>
+      </c>
+      <c r="B946" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C946" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D946" s="12">
+        <v>1</v>
+      </c>
+      <c r="E946" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F946" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G946" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H946" s="16"/>
+    </row>
+    <row r="947" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A947" s="9">
+        <v>68325</v>
+      </c>
+      <c r="B947" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C947" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D947" s="12">
+        <v>6</v>
+      </c>
+      <c r="E947" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F947" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G947" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H947" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="948" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A948" s="9">
+        <v>69416</v>
+      </c>
+      <c r="B948" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C948" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D948" s="12">
+        <v>1</v>
+      </c>
+      <c r="E948" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F948" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G948" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H948" s="16"/>
+    </row>
+    <row r="949" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A949" s="9">
+        <v>70099</v>
+      </c>
+      <c r="B949" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C949" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D949" s="12">
+        <v>1</v>
+      </c>
+      <c r="E949" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F949" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G949" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H949" s="16"/>
+    </row>
+    <row r="950" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A950" s="9">
+        <v>70450</v>
+      </c>
+      <c r="B950" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C950" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D950" s="12">
+        <v>6</v>
+      </c>
+      <c r="E950" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F950" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G950" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H950" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="951" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A951" s="9">
+        <v>70539</v>
+      </c>
+      <c r="B951" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C951" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D951" s="12">
+        <v>1</v>
+      </c>
+      <c r="E951" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F951" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G951" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H951" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="952" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A952" s="9">
+        <v>70137</v>
+      </c>
+      <c r="B952" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C952" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D952" s="12">
+        <v>1</v>
+      </c>
+      <c r="E952" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F952" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G952" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H952" s="16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="953" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A953" s="9">
+        <v>70254</v>
+      </c>
+      <c r="B953" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C953" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D953" s="12">
+        <v>5</v>
+      </c>
+      <c r="E953" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F953" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G953" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H953" s="16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="954" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A954" s="9">
+        <v>70040</v>
+      </c>
+      <c r="B954" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C954" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D954" s="12">
+        <v>1</v>
+      </c>
+      <c r="E954" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F954" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G954" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H954" s="16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="955" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A955" s="9">
+        <v>69698</v>
+      </c>
+      <c r="B955" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C955" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D955" s="12">
+        <v>1</v>
+      </c>
+      <c r="E955" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F955" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G955" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H955" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="956" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A956" s="9">
+        <v>69049</v>
+      </c>
+      <c r="B956" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C956" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D956" s="12">
+        <v>4</v>
+      </c>
+      <c r="E956" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F956" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G956" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H956" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="957" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A957" s="9">
+        <v>70495</v>
+      </c>
+      <c r="B957" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C957" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D957" s="12">
+        <v>1</v>
+      </c>
+      <c r="E957" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F957" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G957" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H957" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="958" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A958" s="9">
+        <v>70299</v>
+      </c>
+      <c r="B958" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C958" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D958" s="12">
+        <v>4</v>
+      </c>
+      <c r="E958" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F958" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G958" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H958" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="959" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A959" s="9">
+        <v>70283</v>
+      </c>
+      <c r="B959" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C959" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D959" s="12">
+        <v>6</v>
+      </c>
+      <c r="E959" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F959" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G959" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H959" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="960" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A960" s="9">
+        <v>70285</v>
+      </c>
+      <c r="B960" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C960" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D960" s="12">
+        <v>4</v>
+      </c>
+      <c r="E960" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F960" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G960" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H960" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="961" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A961" s="9">
+        <v>70289</v>
+      </c>
+      <c r="B961" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C961" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D961" s="12">
+        <v>2</v>
+      </c>
+      <c r="E961" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F961" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G961" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H961" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="962" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A962" s="9">
+        <v>70297</v>
+      </c>
+      <c r="B962" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C962" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D962" s="12">
+        <v>7</v>
+      </c>
+      <c r="E962" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F962" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G962" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H962" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="963" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A963" s="9">
+        <v>70206</v>
+      </c>
+      <c r="B963" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C963" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D963" s="12">
+        <v>3</v>
+      </c>
+      <c r="E963" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F963" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G963" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H963" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="964" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A964" s="9">
+        <v>69683</v>
+      </c>
+      <c r="B964" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C964" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D964" s="12">
+        <v>0</v>
+      </c>
+      <c r="E964" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F964" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G964" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H964" s="16"/>
+    </row>
+    <row r="965" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A965" s="9">
+        <v>70067</v>
+      </c>
+      <c r="B965" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C965" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D965" s="12">
+        <v>0</v>
+      </c>
+      <c r="E965" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F965" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G965" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H965" s="16"/>
+    </row>
+    <row r="966" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A966" s="9">
+        <v>70116</v>
+      </c>
+      <c r="B966" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C966" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D966" s="12">
+        <v>0</v>
+      </c>
+      <c r="E966" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F966" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G966" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H966" s="16"/>
+    </row>
+    <row r="967" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A967" s="9">
+        <v>70110</v>
+      </c>
+      <c r="B967" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C967" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D967" s="12">
+        <v>0</v>
+      </c>
+      <c r="E967" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F967" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G967" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H967" s="16"/>
+    </row>
+    <row r="968" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A968" s="9">
+        <v>70066</v>
+      </c>
+      <c r="B968" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C968" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D968" s="12">
+        <v>0</v>
+      </c>
+      <c r="E968" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F968" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G968" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H968" s="16"/>
+    </row>
+    <row r="969" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A969" s="9">
+        <v>70058</v>
+      </c>
+      <c r="B969" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C969" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D969" s="12">
+        <v>0</v>
+      </c>
+      <c r="E969" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F969" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G969" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H969" s="16"/>
+    </row>
+    <row r="970" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A970" s="9">
+        <v>70057</v>
+      </c>
+      <c r="B970" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C970" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D970" s="12">
+        <v>0</v>
+      </c>
+      <c r="E970" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F970" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G970" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H970" s="16"/>
+    </row>
+    <row r="971" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A971" s="9">
+        <v>68159</v>
+      </c>
+      <c r="B971" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C971" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D971" s="12">
+        <v>0</v>
+      </c>
+      <c r="E971" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F971" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G971" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H971" s="16"/>
+    </row>
+    <row r="972" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A972" s="9">
+        <v>68673</v>
+      </c>
+      <c r="B972" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C972" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D972" s="12">
+        <v>0</v>
+      </c>
+      <c r="E972" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F972" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G972" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H972" s="16"/>
+    </row>
+    <row r="973" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A973" s="9">
+        <v>68157</v>
+      </c>
+      <c r="B973" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C973" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D973" s="12">
+        <v>0</v>
+      </c>
+      <c r="E973" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F973" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G973" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H973" s="16"/>
+    </row>
+    <row r="974" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A974" s="9">
+        <v>69735</v>
+      </c>
+      <c r="B974" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C974" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D974" s="12">
+        <v>2</v>
+      </c>
+      <c r="E974" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F974" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G974" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H974" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="975" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A975" s="9">
+        <v>68158</v>
+      </c>
+      <c r="B975" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C975" s="18">
+        <v>46316</v>
+      </c>
+      <c r="D975" s="12">
+        <v>0</v>
+      </c>
+      <c r="E975" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F975" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G975" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H975" s="16"/>
+    </row>
+    <row r="976" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A976" s="9">
+        <v>70537</v>
+      </c>
+      <c r="B976" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C976" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D976" s="12">
+        <v>2</v>
+      </c>
+      <c r="E976" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F976" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G976" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H976" s="16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="977" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A977" s="9">
+        <v>69897</v>
+      </c>
+      <c r="B977" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C977" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D977" s="12">
+        <v>5</v>
+      </c>
+      <c r="E977" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F977" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G977" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H977" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="978" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A978" s="9">
+        <v>69492</v>
+      </c>
+      <c r="B978" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C978" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D978" s="12">
+        <v>0</v>
+      </c>
+      <c r="E978" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F978" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G978" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H978" s="16"/>
+    </row>
+    <row r="979" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A979" s="9">
+        <v>69863</v>
+      </c>
+      <c r="B979" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C979" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D979" s="12">
+        <v>0</v>
+      </c>
+      <c r="E979" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F979" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G979" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H979" s="16"/>
+    </row>
+    <row r="980" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A980" s="9">
+        <v>69849</v>
+      </c>
+      <c r="B980" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C980" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D980" s="12">
+        <v>0</v>
+      </c>
+      <c r="E980" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F980" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G980" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H980" s="16"/>
+    </row>
+    <row r="981" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A981" s="9">
+        <v>63892</v>
+      </c>
+      <c r="B981" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C981" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D981" s="12">
+        <v>1</v>
+      </c>
+      <c r="E981" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F981" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G981" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H981" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="982" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A982" s="9">
+        <v>70115</v>
+      </c>
+      <c r="B982" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C982" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D982" s="12">
+        <v>0</v>
+      </c>
+      <c r="E982" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F982" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G982" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H982" s="16"/>
+    </row>
+    <row r="983" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A983" s="9">
+        <v>69076</v>
+      </c>
+      <c r="B983" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C983" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D983" s="12">
+        <v>1</v>
+      </c>
+      <c r="E983" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F983" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G983" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H983" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="984" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A984" s="9">
+        <v>70016</v>
+      </c>
+      <c r="B984" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C984" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D984" s="12">
+        <v>4</v>
+      </c>
+      <c r="E984" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F984" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G984" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H984" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="985" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A985" s="9">
+        <v>69220</v>
+      </c>
+      <c r="B985" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C985" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D985" s="12">
+        <v>2</v>
+      </c>
+      <c r="E985" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F985" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G985" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H985" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="986" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A986" s="9">
+        <v>70491</v>
+      </c>
+      <c r="B986" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C986" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D986" s="12">
+        <v>2</v>
+      </c>
+      <c r="E986" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F986" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G986" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H986" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="987" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A987" s="9">
+        <v>69646</v>
+      </c>
+      <c r="B987" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C987" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D987" s="12">
+        <v>1</v>
+      </c>
+      <c r="E987" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F987" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G987" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H987" s="16"/>
+    </row>
+    <row r="988" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A988" s="9">
+        <v>69533</v>
+      </c>
+      <c r="B988" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C988" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D988" s="12">
+        <v>1</v>
+      </c>
+      <c r="E988" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F988" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G988" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H988" s="16"/>
+    </row>
+    <row r="989" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A989" s="9">
+        <v>70476</v>
+      </c>
+      <c r="B989" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C989" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D989" s="12">
+        <v>1</v>
+      </c>
+      <c r="E989" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F989" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G989" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H989" s="16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="990" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A990" s="9">
+        <v>70478</v>
+      </c>
+      <c r="B990" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C990" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D990" s="12">
+        <v>5</v>
+      </c>
+      <c r="E990" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F990" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G990" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H990" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="991" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A991" s="9">
+        <v>70461</v>
+      </c>
+      <c r="B991" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C991" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D991" s="12">
+        <v>3</v>
+      </c>
+      <c r="E991" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F991" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G991" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H991" s="16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="992" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A992" s="9">
+        <v>70469</v>
+      </c>
+      <c r="B992" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C992" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D992" s="12">
+        <v>1</v>
+      </c>
+      <c r="E992" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F992" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G992" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H992" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="993" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A993" s="9">
+        <v>70471</v>
+      </c>
+      <c r="B993" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C993" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D993" s="12">
+        <v>1</v>
+      </c>
+      <c r="E993" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F993" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G993" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H993" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="994" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A994" s="9">
+        <v>70465</v>
+      </c>
+      <c r="B994" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C994" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D994" s="12">
+        <v>1</v>
+      </c>
+      <c r="E994" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F994" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G994" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H994" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="995" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A995" s="9">
+        <v>70472</v>
+      </c>
+      <c r="B995" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C995" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D995" s="12">
+        <v>1</v>
+      </c>
+      <c r="E995" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F995" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G995" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H995" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="996" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A996" s="9">
+        <v>70527</v>
+      </c>
+      <c r="B996" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C996" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D996" s="12">
+        <v>2</v>
+      </c>
+      <c r="E996" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F996" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G996" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H996" s="16"/>
+    </row>
+    <row r="997" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A997" s="9">
+        <v>70546</v>
+      </c>
+      <c r="B997" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C997" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D997" s="12">
+        <v>3</v>
+      </c>
+      <c r="E997" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F997" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G997" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H997" s="16"/>
+    </row>
+    <row r="998" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A998" s="9">
+        <v>68765</v>
+      </c>
+      <c r="B998" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C998" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D998" s="12">
+        <v>2</v>
+      </c>
+      <c r="E998" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F998" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G998" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H998" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="999" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A999" s="9">
+        <v>69043</v>
+      </c>
+      <c r="B999" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C999" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D999" s="12">
+        <v>3</v>
+      </c>
+      <c r="E999" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F999" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G999" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H999" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1000" s="9">
+        <v>68450</v>
+      </c>
+      <c r="B1000" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1000" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1000" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1000" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1000" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1000" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1000" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1001" s="9">
+        <v>66738</v>
+      </c>
+      <c r="B1001" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1001" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1001" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1001" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1001" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1001" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1001" s="16"/>
+    </row>
+    <row r="1002" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1002" s="9">
+        <v>68142</v>
+      </c>
+      <c r="B1002" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1002" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1002" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1002" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1002" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1002" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1002" s="16"/>
+    </row>
+    <row r="1003" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1003" s="9">
+        <v>70193</v>
+      </c>
+      <c r="B1003" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1003" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1003" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1003" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1003" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1003" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1003" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1004" s="9">
+        <v>70449</v>
+      </c>
+      <c r="B1004" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1004" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1004" s="12">
+        <v>5</v>
+      </c>
+      <c r="E1004" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1004" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1004" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1004" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1005" s="9">
+        <v>69205</v>
+      </c>
+      <c r="B1005" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1005" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1005" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1005" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1005" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1005" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1005" s="16"/>
+    </row>
+    <row r="1006" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1006" s="9">
+        <v>70547</v>
+      </c>
+      <c r="B1006" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1006" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1006" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1006" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1006" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1006" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1006" s="16"/>
+    </row>
+    <row r="1007" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1007" s="9">
+        <v>70530</v>
+      </c>
+      <c r="B1007" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1007" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1007" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1007" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1007" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1007" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1007" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1008" s="9">
+        <v>70551</v>
+      </c>
+      <c r="B1008" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1008" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1008" s="12">
+        <v>6</v>
+      </c>
+      <c r="E1008" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1008" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1008" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1008" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A684">
@@ -53543,7 +55434,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="str" cm="1">
-        <f t="array" ref="A1:A15">_xlfn.UNIQUE(DadosBrutos!C1:C935)</f>
+        <f t="array" ref="A1:A16">_xlfn.UNIQUE(DadosBrutos!C1:C1008)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="23" t="s">
@@ -53673,11 +55564,17 @@
       </c>
       <c r="B15" s="22">
         <f>COUNTIF(DadosBrutos!C:C, A15)</f>
-        <v>25</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
+      <c r="A16" s="24">
+        <v>46317</v>
+      </c>
+      <c r="B16" s="22">
+        <f>COUNTIF(DadosBrutos!C:C, A16)</f>
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="24"/>
@@ -55830,7 +57727,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="str" cm="1">
-        <f t="array" ref="A1:A15">_xlfn.UNIQUE(DadosBrutos!C1:C935)</f>
+        <f t="array" ref="A1:A16">_xlfn.UNIQUE(DadosBrutos!C1:C1008)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="23" t="s">
@@ -56015,15 +57912,25 @@
       </c>
       <c r="B15">
         <f>COUNTIFS(DadosBrutos!C:C, A15, DadosBrutos!G:G, "SAUDAVEL")</f>
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <f>COUNTIFS(DadosBrutos!C:C, A15, DadosBrutos!G:G, "BACKLOG")</f>
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
+      <c r="A16" s="24">
+        <v>46317</v>
+      </c>
+      <c r="B16">
+        <f>COUNTIFS(DadosBrutos!C:C, A16, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <f>COUNTIFS(DadosBrutos!C:C, A16, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>24</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="24"/>

--- a/DadosProducao.xlsx
+++ b/DadosProducao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A978BDAA-FAB8-4C4E-8523-6C8962F8B57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBFF59B-0B5B-4977-887D-E25CDE5CCFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
   </bookViews>
   <sheets>
     <sheet name="DadosBrutos" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4291" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4715" uniqueCount="197">
   <si>
     <t>PV</t>
   </si>
@@ -586,6 +586,96 @@
   <si>
     <t>NATHALIE</t>
   </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>DASA BARUERI</t>
+  </si>
+  <si>
+    <t>DASA 61.486.650/0030</t>
+  </si>
+  <si>
+    <t>DASA IPIRANGA</t>
+  </si>
+  <si>
+    <t>TECNOLAB UNIDADE XI</t>
+  </si>
+  <si>
+    <t>TEC LAB 51.131.969/0</t>
+  </si>
+  <si>
+    <t>TECNOLAB UNIDADE X</t>
+  </si>
+  <si>
+    <t>TECNOLAB UNIDADE IX</t>
+  </si>
+  <si>
+    <t>HOSPITAL SANTA RITA</t>
+  </si>
+  <si>
+    <t>MATRIZ</t>
+  </si>
+  <si>
+    <t>HOSPITAL QUINTA DOR</t>
+  </si>
+  <si>
+    <t>HOSPITAL BALBINO</t>
+  </si>
+  <si>
+    <t>CORREIOS</t>
+  </si>
+  <si>
+    <t>DASA FORTALEZA</t>
+  </si>
+  <si>
+    <t>HOSPITAL SAO JOSE</t>
+  </si>
+  <si>
+    <t>LIDERANCA SP</t>
+  </si>
+  <si>
+    <t>SECONCI CENTRO</t>
+  </si>
+  <si>
+    <t>SYNGENTA PROTECAO</t>
+  </si>
+  <si>
+    <t>HOSP INFANTIL SABARA</t>
+  </si>
+  <si>
+    <t>INFANTE DOM HENRIQUE</t>
+  </si>
+  <si>
+    <t>DASA 12.857.736/0001</t>
+  </si>
+  <si>
+    <t>DASA SALVADORBA</t>
+  </si>
+  <si>
+    <t>NAYARA</t>
+  </si>
+  <si>
+    <t>HOSP SAO LUCAS</t>
+  </si>
+  <si>
+    <t>DASA LAB NOBEL S.</t>
+  </si>
+  <si>
+    <t>CLEANING SOLUTIONS C</t>
+  </si>
+  <si>
+    <t>DASA ITAIM BIBI</t>
+  </si>
+  <si>
+    <t>DASA SP</t>
+  </si>
+  <si>
+    <t>AMPARO MATERNAL SPDM</t>
+  </si>
+  <si>
+    <t>HSM ALAMEDA SANTOS</t>
+  </si>
 </sst>
 </file>
 
@@ -709,7 +799,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -767,6 +857,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9946F4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -900,7 +1008,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -952,6 +1060,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28221,7 +28334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B0C76F-2D49-44D6-9EF1-05536D6E01AD}">
-  <dimension ref="A1:H1008"/>
+  <dimension ref="A1:I1097"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -55377,6 +55490,2367 @@
         <v>14</v>
       </c>
       <c r="H1008" s="16"/>
+    </row>
+    <row r="1009" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1009" s="9">
+        <v>70558</v>
+      </c>
+      <c r="B1009" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1009" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1009" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1009" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1009" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1009" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1009" s="33"/>
+      <c r="I1009" s="34"/>
+    </row>
+    <row r="1010" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1010" s="9">
+        <v>70048</v>
+      </c>
+      <c r="B1010" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1010" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1010" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1010" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1010" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1010" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1010" s="33"/>
+      <c r="I1010" s="34"/>
+    </row>
+    <row r="1011" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1011" s="9">
+        <v>70518</v>
+      </c>
+      <c r="B1011" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1011" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1011" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1011" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1011" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1011" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1011" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1011" s="34"/>
+    </row>
+    <row r="1012" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1012" s="9">
+        <v>70526</v>
+      </c>
+      <c r="B1012" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1012" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1012" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1012" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1012" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1012" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1012" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1012" s="34"/>
+    </row>
+    <row r="1013" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1013" s="9">
+        <v>70528</v>
+      </c>
+      <c r="B1013" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1013" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1013" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1013" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1013" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1013" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1013" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1013" s="34"/>
+    </row>
+    <row r="1014" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1014" s="9">
+        <v>70529</v>
+      </c>
+      <c r="B1014" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1014" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1014" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1014" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1014" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1014" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1014" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1014" s="34"/>
+    </row>
+    <row r="1015" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1015" s="9">
+        <v>70494</v>
+      </c>
+      <c r="B1015" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1015" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1015" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1015" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1015" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1015" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1015" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1015" s="34"/>
+    </row>
+    <row r="1016" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1016" s="9">
+        <v>70490</v>
+      </c>
+      <c r="B1016" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1016" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1016" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1016" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1016" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1016" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1016" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1016" s="34"/>
+    </row>
+    <row r="1017" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1017" s="9">
+        <v>68825</v>
+      </c>
+      <c r="B1017" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1017" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1017" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1017" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1017" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1017" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1017" s="16"/>
+      <c r="I1017" s="34"/>
+    </row>
+    <row r="1018" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1018" s="9">
+        <v>70056</v>
+      </c>
+      <c r="B1018" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1018" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1018" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1018" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1018" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1018" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1018" s="16"/>
+      <c r="I1018" s="34"/>
+    </row>
+    <row r="1019" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1019" s="9">
+        <v>70486</v>
+      </c>
+      <c r="B1019" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1019" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1019" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1019" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1019" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1019" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1019" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1019" s="34"/>
+    </row>
+    <row r="1020" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1020" s="9">
+        <v>70489</v>
+      </c>
+      <c r="B1020" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1020" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1020" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1020" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1020" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1020" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1020" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1020" s="34"/>
+    </row>
+    <row r="1021" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1021" s="9">
+        <v>70485</v>
+      </c>
+      <c r="B1021" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1021" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1021" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1021" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1021" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1021" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1021" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1021" s="34"/>
+    </row>
+    <row r="1022" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1022" s="9">
+        <v>70483</v>
+      </c>
+      <c r="B1022" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1022" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1022" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1022" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1022" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1022" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1022" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1022" s="34"/>
+    </row>
+    <row r="1023" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1023" s="9">
+        <v>70477</v>
+      </c>
+      <c r="B1023" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1023" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1023" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1023" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1023" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1023" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1023" s="16"/>
+      <c r="I1023" s="34"/>
+    </row>
+    <row r="1024" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1024" s="9">
+        <v>70475</v>
+      </c>
+      <c r="B1024" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1024" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1024" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1024" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1024" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1024" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1024" s="16"/>
+      <c r="I1024" s="34"/>
+    </row>
+    <row r="1025" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1025" s="9">
+        <v>65954</v>
+      </c>
+      <c r="B1025" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1025" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1025" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1025" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1025" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1025" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1025" s="16"/>
+      <c r="I1025" s="34"/>
+    </row>
+    <row r="1026" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1026" s="9">
+        <v>70202</v>
+      </c>
+      <c r="B1026" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1026" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1026" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1026" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1026" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1026" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1026" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="I1026" s="34"/>
+    </row>
+    <row r="1027" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1027" s="9">
+        <v>69957</v>
+      </c>
+      <c r="B1027" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1027" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1027" s="12">
+        <v>5</v>
+      </c>
+      <c r="E1027" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1027" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1027" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1027" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1027" s="34"/>
+    </row>
+    <row r="1028" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1028" s="9">
+        <v>70240</v>
+      </c>
+      <c r="B1028" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1028" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1028" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1028" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1028" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1028" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1028" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1028" s="34"/>
+    </row>
+    <row r="1029" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1029" s="9">
+        <v>70194</v>
+      </c>
+      <c r="B1029" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1029" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1029" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1029" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1029" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1029" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1029" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1029" s="34"/>
+    </row>
+    <row r="1030" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1030" s="9">
+        <v>69815</v>
+      </c>
+      <c r="B1030" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1030" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1030" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1030" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1030" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1030" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1030" s="16"/>
+      <c r="I1030" s="34"/>
+    </row>
+    <row r="1031" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1031" s="9">
+        <v>70511</v>
+      </c>
+      <c r="B1031" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1031" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1031" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1031" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1031" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1031" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1031" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1031" s="34"/>
+    </row>
+    <row r="1032" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1032" s="9">
+        <v>70448</v>
+      </c>
+      <c r="B1032" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1032" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1032" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1032" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1032" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1032" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1032" s="16"/>
+      <c r="I1032" s="34"/>
+    </row>
+    <row r="1033" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1033" s="9">
+        <v>70212</v>
+      </c>
+      <c r="B1033" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1033" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1033" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1033" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1033" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1033" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1033" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1033" s="34"/>
+    </row>
+    <row r="1034" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1034" s="9">
+        <v>70034</v>
+      </c>
+      <c r="B1034" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1034" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1034" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1034" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1034" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1034" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1034" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1034" s="34"/>
+    </row>
+    <row r="1035" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1035" s="9">
+        <v>70308</v>
+      </c>
+      <c r="B1035" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1035" s="31">
+        <v>46317</v>
+      </c>
+      <c r="D1035" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1035" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1035" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1035" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1035" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1035" s="34"/>
+    </row>
+    <row r="1036" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1036" s="9">
+        <v>70094</v>
+      </c>
+      <c r="B1036" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1036" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1036" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1036" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1036" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1036" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1036" s="16"/>
+      <c r="I1036" s="34"/>
+    </row>
+    <row r="1037" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1037" s="9">
+        <v>70504</v>
+      </c>
+      <c r="B1037" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1037" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1037" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1037" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1037" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1037" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1037" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1037" s="34"/>
+    </row>
+    <row r="1038" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1038" s="9">
+        <v>69791</v>
+      </c>
+      <c r="B1038" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1038" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1038" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1038" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1038" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1038" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1038" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1038" s="34"/>
+    </row>
+    <row r="1039" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1039" s="9">
+        <v>70253</v>
+      </c>
+      <c r="B1039" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1039" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1039" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1039" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1039" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1039" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1039" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1039" s="34"/>
+    </row>
+    <row r="1040" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1040" s="9">
+        <v>69788</v>
+      </c>
+      <c r="B1040" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1040" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1040" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1040" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1040" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1040" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1040" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1040" s="34"/>
+    </row>
+    <row r="1041" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1041" s="9">
+        <v>70514</v>
+      </c>
+      <c r="B1041" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1041" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1041" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1041" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1041" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1041" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1041" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1041" s="34"/>
+    </row>
+    <row r="1042" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1042" s="9">
+        <v>70313</v>
+      </c>
+      <c r="B1042" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1042" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1042" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1042" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1042" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1042" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1042" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1042" s="34"/>
+    </row>
+    <row r="1043" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1043" s="9">
+        <v>70244</v>
+      </c>
+      <c r="B1043" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1043" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1043" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1043" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1043" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1043" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1043" s="16"/>
+      <c r="I1043" s="34"/>
+    </row>
+    <row r="1044" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1044" s="27">
+        <v>70243</v>
+      </c>
+      <c r="B1044" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1044" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1044" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1044" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1044" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1044" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1044" s="16"/>
+      <c r="I1044" s="34"/>
+    </row>
+    <row r="1045" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1045" s="27">
+        <v>70151</v>
+      </c>
+      <c r="B1045" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1045" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1045" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1045" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1045" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1045" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1045" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1045" s="34"/>
+    </row>
+    <row r="1046" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1046" s="9">
+        <v>70218</v>
+      </c>
+      <c r="B1046" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1046" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1046" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1046" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1046" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1046" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1046" s="16"/>
+      <c r="I1046" s="34"/>
+    </row>
+    <row r="1047" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1047" s="9">
+        <v>70231</v>
+      </c>
+      <c r="B1047" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1047" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1047" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1047" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1047" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1047" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1047" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1047" s="34"/>
+    </row>
+    <row r="1048" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1048" s="9">
+        <v>70168</v>
+      </c>
+      <c r="B1048" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1048" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1048" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1048" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1048" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1048" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1048" s="16"/>
+      <c r="I1048" s="34"/>
+    </row>
+    <row r="1049" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1049" s="9">
+        <v>70167</v>
+      </c>
+      <c r="B1049" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1049" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1049" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1049" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1049" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1049" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1049" s="16"/>
+      <c r="I1049" s="34"/>
+    </row>
+    <row r="1050" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1050" s="9">
+        <v>70140</v>
+      </c>
+      <c r="B1050" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1050" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1050" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1050" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1050" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1050" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1050" s="16"/>
+      <c r="I1050" s="34"/>
+    </row>
+    <row r="1051" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1051" s="9">
+        <v>69727</v>
+      </c>
+      <c r="B1051" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1051" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1051" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1051" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1051" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1051" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1051" s="16"/>
+      <c r="I1051" s="34"/>
+    </row>
+    <row r="1052" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1052" s="9">
+        <v>70242</v>
+      </c>
+      <c r="B1052" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1052" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1052" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1052" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1052" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1052" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1052" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1052" s="34"/>
+    </row>
+    <row r="1053" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1053" s="27">
+        <v>68726</v>
+      </c>
+      <c r="B1053" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1053" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1053" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1053" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1053" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1053" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1053" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1053" s="34"/>
+    </row>
+    <row r="1054" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1054" s="27">
+        <v>69856</v>
+      </c>
+      <c r="B1054" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1054" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1054" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1054" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1054" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1054" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1054" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1054" s="34"/>
+    </row>
+    <row r="1055" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1055" s="9">
+        <v>70562</v>
+      </c>
+      <c r="B1055" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1055" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1055" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1055" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1055" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1055" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1055" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1055" s="34"/>
+    </row>
+    <row r="1056" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1056" s="9">
+        <v>60105</v>
+      </c>
+      <c r="B1056" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1056" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1056" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1056" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1056" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1056" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1056" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1056" s="34"/>
+    </row>
+    <row r="1057" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1057" s="9">
+        <v>68165</v>
+      </c>
+      <c r="B1057" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1057" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1057" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1057" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1057" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1057" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1057" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1057" s="34"/>
+    </row>
+    <row r="1058" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1058" s="9">
+        <v>67323</v>
+      </c>
+      <c r="B1058" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1058" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1058" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1058" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1058" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1058" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1058" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1058" s="34"/>
+    </row>
+    <row r="1059" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1059" s="9">
+        <v>68463</v>
+      </c>
+      <c r="B1059" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1059" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1059" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1059" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1059" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1059" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1059" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1059" s="34"/>
+    </row>
+    <row r="1060" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1060" s="9">
+        <v>66604</v>
+      </c>
+      <c r="B1060" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1060" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1060" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1060" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1060" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1060" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1060" s="16"/>
+      <c r="I1060" s="34"/>
+    </row>
+    <row r="1061" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1061" s="9">
+        <v>69443</v>
+      </c>
+      <c r="B1061" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1061" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1061" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1061" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1061" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1061" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1061" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1061" s="34"/>
+    </row>
+    <row r="1062" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1062" s="9">
+        <v>69147</v>
+      </c>
+      <c r="B1062" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1062" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1062" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1062" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1062" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1062" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1062" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1062" s="34"/>
+    </row>
+    <row r="1063" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1063" s="9">
+        <v>69947</v>
+      </c>
+      <c r="B1063" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1063" s="18">
+        <v>46317</v>
+      </c>
+      <c r="D1063" s="12">
+        <v>13</v>
+      </c>
+      <c r="E1063" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1063" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1063" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1063" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I1063" s="34"/>
+    </row>
+    <row r="1064" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1064" s="9">
+        <v>69960</v>
+      </c>
+      <c r="B1064" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1064" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1064" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1064" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1064" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1064" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1064" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1064" s="34"/>
+    </row>
+    <row r="1065" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1065" s="27">
+        <v>65142</v>
+      </c>
+      <c r="B1065" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1065" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1065" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1065" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1065" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1065" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1065" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="I1065" s="34"/>
+    </row>
+    <row r="1066" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1066" s="9">
+        <v>64514</v>
+      </c>
+      <c r="B1066" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1066" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1066" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1066" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1066" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1066" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1066" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1066" s="34"/>
+    </row>
+    <row r="1067" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1067" s="27">
+        <v>68726</v>
+      </c>
+      <c r="B1067" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1067" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1067" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1067" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1067" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1067" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1067" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1067" s="34"/>
+    </row>
+    <row r="1068" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1068" s="27">
+        <v>68942</v>
+      </c>
+      <c r="B1068" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1068" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1068" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1068" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1068" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1068" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1068" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1068" s="34"/>
+    </row>
+    <row r="1069" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1069" s="9">
+        <v>70507</v>
+      </c>
+      <c r="B1069" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1069" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1069" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1069" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1069" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1069" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1069" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1069" s="34"/>
+    </row>
+    <row r="1070" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1070" s="9">
+        <v>69171</v>
+      </c>
+      <c r="B1070" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1070" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1070" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1070" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1070" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1070" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1070" s="16"/>
+      <c r="I1070" s="34"/>
+    </row>
+    <row r="1071" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1071" s="9">
+        <v>70451</v>
+      </c>
+      <c r="B1071" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1071" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1071" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1071" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1071" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1071" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1071" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1071" s="34"/>
+    </row>
+    <row r="1072" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1072" s="9">
+        <v>70559</v>
+      </c>
+      <c r="B1072" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1072" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1072" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1072" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1072" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1072" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1072" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1072" s="34"/>
+    </row>
+    <row r="1073" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1073" s="9">
+        <v>70545</v>
+      </c>
+      <c r="B1073" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1073" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1073" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1073" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1073" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1073" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1073" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1073" s="34"/>
+    </row>
+    <row r="1074" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1074" s="9">
+        <v>70385</v>
+      </c>
+      <c r="B1074" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1074" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1074" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1074" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1074" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1074" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1074" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1074" s="34"/>
+    </row>
+    <row r="1075" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1075" s="9">
+        <v>70148</v>
+      </c>
+      <c r="B1075" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1075" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1075" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1075" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1075" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1075" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1075" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1075" s="34"/>
+    </row>
+    <row r="1076" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1076" s="9">
+        <v>70189</v>
+      </c>
+      <c r="B1076" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1076" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1076" s="12">
+        <v>9</v>
+      </c>
+      <c r="E1076" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1076" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1076" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1076" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1076" s="34"/>
+    </row>
+    <row r="1077" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1077" s="9">
+        <v>70191</v>
+      </c>
+      <c r="B1077" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1077" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1077" s="12">
+        <v>8</v>
+      </c>
+      <c r="E1077" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1077" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1077" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1077" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1077" s="34"/>
+    </row>
+    <row r="1078" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1078" s="9">
+        <v>70565</v>
+      </c>
+      <c r="B1078" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1078" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1078" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1078" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1078" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1078" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1078" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1078" s="34"/>
+    </row>
+    <row r="1079" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1079" s="9">
+        <v>70566</v>
+      </c>
+      <c r="B1079" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1079" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1079" s="12">
+        <v>7</v>
+      </c>
+      <c r="E1079" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1079" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1079" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1079" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I1079" s="34"/>
+    </row>
+    <row r="1080" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1080" s="9">
+        <v>70564</v>
+      </c>
+      <c r="B1080" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1080" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1080" s="12">
+        <v>19</v>
+      </c>
+      <c r="E1080" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1080" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1080" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1080" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="I1080" s="34"/>
+    </row>
+    <row r="1081" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1081" s="9">
+        <v>70650</v>
+      </c>
+      <c r="B1081" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1081" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1081" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1081" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1081" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1081" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1081" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1081" s="34"/>
+    </row>
+    <row r="1082" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1082" s="9">
+        <v>70567</v>
+      </c>
+      <c r="B1082" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1082" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1082" s="12">
+        <v>8</v>
+      </c>
+      <c r="E1082" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1082" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1082" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1082" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1082" s="34"/>
+    </row>
+    <row r="1083" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1083" s="9">
+        <v>70579</v>
+      </c>
+      <c r="B1083" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1083" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1083" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1083" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1083" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1083" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1083" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1083" s="34"/>
+    </row>
+    <row r="1084" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1084" s="9">
+        <v>69925</v>
+      </c>
+      <c r="B1084" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1084" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1084" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1084" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1084" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1084" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1084" s="16"/>
+      <c r="I1084" s="34"/>
+    </row>
+    <row r="1085" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1085" s="9">
+        <v>70570</v>
+      </c>
+      <c r="B1085" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1085" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1085" s="12">
+        <v>17</v>
+      </c>
+      <c r="E1085" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1085" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1085" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1085" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1085" s="34"/>
+    </row>
+    <row r="1086" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1086" s="9">
+        <v>70629</v>
+      </c>
+      <c r="B1086" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1086" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1086" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1086" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1086" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1086" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1086" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1086" s="34"/>
+    </row>
+    <row r="1087" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1087" s="9">
+        <v>70561</v>
+      </c>
+      <c r="B1087" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1087" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1087" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1087" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1087" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1087" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1087" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1087" s="34"/>
+    </row>
+    <row r="1088" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1088" s="9">
+        <v>70550</v>
+      </c>
+      <c r="B1088" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1088" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1088" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1088" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1088" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1088" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1088" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1088" s="34"/>
+    </row>
+    <row r="1089" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1089" s="9">
+        <v>70577</v>
+      </c>
+      <c r="B1089" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1089" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1089" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1089" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1089" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1089" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1089" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1089" s="34"/>
+    </row>
+    <row r="1090" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1090" s="9">
+        <v>70602</v>
+      </c>
+      <c r="B1090" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1090" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1090" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1090" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1090" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1090" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1090" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1090" s="34"/>
+    </row>
+    <row r="1091" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1091" s="9">
+        <v>70603</v>
+      </c>
+      <c r="B1091" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1091" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1091" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1091" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1091" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1091" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1091" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="I1091" s="34"/>
+    </row>
+    <row r="1092" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1092" s="9">
+        <v>70587</v>
+      </c>
+      <c r="B1092" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1092" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1092" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1092" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1092" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1092" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1092" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1092" s="34"/>
+    </row>
+    <row r="1093" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1093" s="9">
+        <v>70591</v>
+      </c>
+      <c r="B1093" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1093" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1093" s="12">
+        <v>1</v>
+      </c>
+      <c r="E1093" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1093" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1093" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1093" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1093" s="34"/>
+    </row>
+    <row r="1094" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1094" s="9">
+        <v>70555</v>
+      </c>
+      <c r="B1094" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1094" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1094" s="12">
+        <v>4</v>
+      </c>
+      <c r="E1094" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1094" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1094" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1094" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1094" s="34"/>
+    </row>
+    <row r="1095" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1095" s="9">
+        <v>70524</v>
+      </c>
+      <c r="B1095" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1095" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1095" s="12">
+        <v>2</v>
+      </c>
+      <c r="E1095" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1095" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1095" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1095" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1095" s="34"/>
+    </row>
+    <row r="1096" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1096" s="9">
+        <v>69579</v>
+      </c>
+      <c r="B1096" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1096" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1096" s="12">
+        <v>0</v>
+      </c>
+      <c r="E1096" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1096" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1096" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1096" s="16"/>
+      <c r="I1096" s="34"/>
+    </row>
+    <row r="1097" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1097" s="27">
+        <v>69542</v>
+      </c>
+      <c r="B1097" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1097" s="18">
+        <v>46318</v>
+      </c>
+      <c r="D1097" s="12">
+        <v>7</v>
+      </c>
+      <c r="E1097" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1097" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1097" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1097" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1097" s="34"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A684">
@@ -55434,7 +57908,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="str" cm="1">
-        <f t="array" ref="A1:A16">_xlfn.UNIQUE(DadosBrutos!C1:C1008)</f>
+        <f t="array" ref="A1:A17">_xlfn.UNIQUE(DadosBrutos!C1:C1097)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="23" t="s">
@@ -55573,55 +58047,61 @@
       </c>
       <c r="B16" s="22">
         <f>COUNTIF(DadosBrutos!C:C, A16)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="24">
+        <v>46318</v>
+      </c>
+      <c r="B17" s="22">
+        <f>COUNTIF(DadosBrutos!C:C, A17)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="24"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="24"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="24"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="24"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="24"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="24"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="24"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="24"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="24"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="24"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
@@ -57727,7 +60207,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="str" cm="1">
-        <f t="array" ref="A1:A16">_xlfn.UNIQUE(DadosBrutos!C1:C1008)</f>
+        <f t="array" ref="A1:A17">_xlfn.UNIQUE(DadosBrutos!C1:C1097)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="23" t="s">
@@ -57925,59 +60405,69 @@
       </c>
       <c r="B16">
         <f>COUNTIFS(DadosBrutos!C:C, A16, DadosBrutos!G:G, "SAUDAVEL")</f>
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C16">
         <f>COUNTIFS(DadosBrutos!C:C, A16, DadosBrutos!G:G, "BACKLOG")</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="24">
+        <v>46318</v>
+      </c>
+      <c r="B17">
+        <f>COUNTIFS(DadosBrutos!C:C, A17, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>28</v>
+      </c>
+      <c r="C17">
+        <f>COUNTIFS(DadosBrutos!C:C, A17, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="24"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="24"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="24"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="24"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="24"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="24"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="24"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="24"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="24"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="24"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">

--- a/DadosProducao.xlsx
+++ b/DadosProducao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D347B0F8-E786-4F3C-9C1F-6E46E18E9168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1FAB18-44D2-4ADA-B1F9-7FFBBB5AEF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
   </bookViews>
   <sheets>
     <sheet name="DadosBrutos" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1361,86 +1361,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color rgb="FFFF33CC"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FF8F098C"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color rgb="FF35DFCF"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FF92D050"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF32FC00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <b/>
@@ -1526,10 +1447,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -35046,19 +34963,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="MATERIAL FALTANDO">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="MATERIAL FALTANDO">
       <formula>NOT(ISERROR(SEARCH("MATERIAL FALTANDO",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="FATURADO">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="FATURADO">
       <formula>NOT(ISERROR(SEARCH("FATURADO",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="CONFERIDO">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="CONFERIDO">
       <formula>NOT(ISERROR(SEARCH("CONFERIDO",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="SEPARANDO">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="SEPARANDO">
       <formula>NOT(ISERROR(SEARCH("SEPARANDO",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35077,7 +34994,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="str" cm="1">
-        <f t="array" ref="A1:A19">_xlfn.UNIQUE(DadosBrutos!C1:C1159)</f>
+        <f t="array" ref="A1:A20">_xlfn.UNIQUE(DadosBrutos!C1:C1273)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="19" t="s">
@@ -35247,7 +35164,13 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
+      <c r="A20" s="20">
+        <v>46322</v>
+      </c>
+      <c r="B20" s="18">
+        <f>COUNTIF(DadosBrutos!C:C, A20)</f>
+        <v>27</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="20"/>
@@ -37388,7 +37311,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="str" cm="1">
-        <f t="array" ref="A1:A19">_xlfn.UNIQUE(DadosBrutos!C1:C1159)</f>
+        <f t="array" ref="A1:A20">_xlfn.UNIQUE(DadosBrutos!C1:C1273)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="19" t="s">
@@ -37633,7 +37556,17 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
+      <c r="A20" s="20">
+        <v>46322</v>
+      </c>
+      <c r="B20">
+        <f>COUNTIFS(DadosBrutos!C:C, A20, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <f>COUNTIFS(DadosBrutos!C:C, A20, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="20"/>

--- a/DadosProducao.xlsx
+++ b/DadosProducao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1FAB18-44D2-4ADA-B1F9-7FFBBB5AEF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BDD791-E09C-49A8-867A-F235AB76B15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5766" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6030" uniqueCount="300">
   <si>
     <t>PV</t>
   </si>
@@ -961,6 +961,9 @@
   <si>
     <t>INSTITUTO HOC</t>
   </si>
+  <si>
+    <t>CONFERIDO</t>
+  </si>
 </sst>
 </file>
 
@@ -1084,7 +1087,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1166,6 +1169,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC1F0C8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1299,7 +1314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1357,6 +1372,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1766,7 +1786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B0C76F-2D49-44D6-9EF1-05536D6E01AD}">
-  <dimension ref="A1:I1273"/>
+  <dimension ref="A1:I1351"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -33834,7 +33854,9 @@
       <c r="A1219" s="9">
         <v>70598</v>
       </c>
-      <c r="B1219" s="13"/>
+      <c r="B1219" s="27" t="s">
+        <v>41</v>
+      </c>
       <c r="C1219" s="14">
         <v>46321</v>
       </c>
@@ -33851,7 +33873,9 @@
       <c r="A1220" s="9">
         <v>70658</v>
       </c>
-      <c r="B1220" s="13"/>
+      <c r="B1220" s="27" t="s">
+        <v>41</v>
+      </c>
       <c r="C1220" s="14">
         <v>46321</v>
       </c>
@@ -34960,6 +34984,1778 @@
       <c r="G1273" s="24"/>
       <c r="H1273" s="12"/>
       <c r="I1273" s="32"/>
+    </row>
+    <row r="1274" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1274" s="23">
+        <v>69326</v>
+      </c>
+      <c r="B1274" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1274" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1274" s="10">
+        <v>6</v>
+      </c>
+      <c r="E1274" s="11"/>
+      <c r="F1274" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1274" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1274" s="32"/>
+    </row>
+    <row r="1275" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1275" s="23">
+        <v>69765</v>
+      </c>
+      <c r="B1275" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1275" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1275" s="10">
+        <v>5</v>
+      </c>
+      <c r="E1275" s="11"/>
+      <c r="F1275" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1275" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1275" s="32"/>
+    </row>
+    <row r="1276" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1276" s="23">
+        <v>69773</v>
+      </c>
+      <c r="B1276" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1276" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1276" s="10">
+        <v>8</v>
+      </c>
+      <c r="E1276" s="11"/>
+      <c r="F1276" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1276" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1276" s="32"/>
+    </row>
+    <row r="1277" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1277" s="23">
+        <v>70565</v>
+      </c>
+      <c r="B1277" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1277" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1277" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1277" s="11"/>
+      <c r="F1277" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1277" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1277" s="32"/>
+    </row>
+    <row r="1278" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1278" s="23">
+        <v>69775</v>
+      </c>
+      <c r="B1278" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1278" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1278" s="10">
+        <v>10</v>
+      </c>
+      <c r="E1278" s="11"/>
+      <c r="F1278" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1278" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1278" s="32"/>
+    </row>
+    <row r="1279" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1279" s="23">
+        <v>69858</v>
+      </c>
+      <c r="B1279" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1279" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1279" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1279" s="11"/>
+      <c r="F1279" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1279" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1279" s="32"/>
+    </row>
+    <row r="1280" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1280" s="23">
+        <v>70070</v>
+      </c>
+      <c r="B1280" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1280" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1280" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1280" s="11"/>
+      <c r="F1280" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1280" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1280" s="32"/>
+    </row>
+    <row r="1281" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1281" s="23">
+        <v>67592</v>
+      </c>
+      <c r="B1281" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1281" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1281" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1281" s="11"/>
+      <c r="F1281" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1281" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1281" s="32"/>
+    </row>
+    <row r="1282" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1282" s="9">
+        <v>70746</v>
+      </c>
+      <c r="B1282" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1282" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1282" s="10">
+        <v>2</v>
+      </c>
+      <c r="E1282" s="11"/>
+      <c r="F1282" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1282" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1282" s="32"/>
+    </row>
+    <row r="1283" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1283" s="23">
+        <v>69887</v>
+      </c>
+      <c r="B1283" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1283" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1283" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1283" s="11"/>
+      <c r="F1283" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1283" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1283" s="32"/>
+    </row>
+    <row r="1284" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1284" s="9">
+        <v>69658</v>
+      </c>
+      <c r="B1284" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1284" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1284" s="10">
+        <v>8</v>
+      </c>
+      <c r="E1284" s="11"/>
+      <c r="F1284" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1284" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1284" s="32"/>
+    </row>
+    <row r="1285" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1285" s="23">
+        <v>67821</v>
+      </c>
+      <c r="B1285" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1285" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1285" s="10">
+        <v>7</v>
+      </c>
+      <c r="E1285" s="11"/>
+      <c r="F1285" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1285" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1285" s="32"/>
+    </row>
+    <row r="1286" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1286" s="23">
+        <v>70168</v>
+      </c>
+      <c r="B1286" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1286" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1286" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1286" s="11"/>
+      <c r="F1286" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1286" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1286" s="32"/>
+    </row>
+    <row r="1287" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1287" s="23">
+        <v>69861</v>
+      </c>
+      <c r="B1287" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1287" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1287" s="10">
+        <v>4</v>
+      </c>
+      <c r="E1287" s="11"/>
+      <c r="F1287" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1287" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1287" s="32"/>
+    </row>
+    <row r="1288" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1288" s="9">
+        <v>67112</v>
+      </c>
+      <c r="B1288" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1288" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1288" s="10">
+        <v>25</v>
+      </c>
+      <c r="E1288" s="11"/>
+      <c r="F1288" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1288" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1288" s="32"/>
+    </row>
+    <row r="1289" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1289" s="23">
+        <v>67106</v>
+      </c>
+      <c r="B1289" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1289" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1289" s="10">
+        <v>24</v>
+      </c>
+      <c r="E1289" s="11"/>
+      <c r="F1289" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1289" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1289" s="32"/>
+    </row>
+    <row r="1290" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1290" s="23">
+        <v>67097</v>
+      </c>
+      <c r="B1290" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1290" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1290" s="10">
+        <v>2</v>
+      </c>
+      <c r="E1290" s="11"/>
+      <c r="F1290" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1290" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1290" s="32"/>
+    </row>
+    <row r="1291" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1291" s="23">
+        <v>69952</v>
+      </c>
+      <c r="B1291" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1291" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1291" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1291" s="11"/>
+      <c r="F1291" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1291" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1291" s="32"/>
+    </row>
+    <row r="1292" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1292" s="23">
+        <v>69804</v>
+      </c>
+      <c r="B1292" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1292" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1292" s="10">
+        <v>9</v>
+      </c>
+      <c r="E1292" s="11"/>
+      <c r="F1292" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1292" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1292" s="32"/>
+    </row>
+    <row r="1293" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1293" s="9">
+        <v>70892</v>
+      </c>
+      <c r="B1293" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1293" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1293" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1293" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1293" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1293" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1293" s="32"/>
+    </row>
+    <row r="1294" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1294" s="9">
+        <v>70825</v>
+      </c>
+      <c r="B1294" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1294" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1294" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1294" s="11"/>
+      <c r="F1294" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1294" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1294" s="32"/>
+    </row>
+    <row r="1295" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1295" s="23">
+        <v>70821</v>
+      </c>
+      <c r="B1295" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1295" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1295" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1295" s="11"/>
+      <c r="F1295" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1295" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1295" s="32"/>
+    </row>
+    <row r="1296" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1296" s="9">
+        <v>70676</v>
+      </c>
+      <c r="B1296" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1296" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1296" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1296" s="11"/>
+      <c r="F1296" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1296" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1296" s="32"/>
+    </row>
+    <row r="1297" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1297" s="9">
+        <v>70829</v>
+      </c>
+      <c r="B1297" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1297" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1297" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1297" s="11"/>
+      <c r="F1297" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1297" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1297" s="32"/>
+    </row>
+    <row r="1298" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1298" s="9">
+        <v>69350</v>
+      </c>
+      <c r="B1298" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1298" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1298" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1298" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1298" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1298" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1298" s="32"/>
+    </row>
+    <row r="1299" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1299" s="23">
+        <v>67821</v>
+      </c>
+      <c r="B1299" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1299" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1299" s="10">
+        <v>7</v>
+      </c>
+      <c r="E1299" s="11"/>
+      <c r="F1299" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1299" s="24"/>
+      <c r="H1299" s="32"/>
+    </row>
+    <row r="1300" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1300" s="23">
+        <v>68740</v>
+      </c>
+      <c r="B1300" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1300" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1300" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1300" s="11"/>
+      <c r="F1300" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1300" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1300" s="32"/>
+    </row>
+    <row r="1301" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1301" s="9">
+        <v>69035</v>
+      </c>
+      <c r="B1301" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1301" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1301" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1301" s="11"/>
+      <c r="F1301" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1301" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1301" s="32"/>
+    </row>
+    <row r="1302" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1302" s="23">
+        <v>69234</v>
+      </c>
+      <c r="B1302" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1302" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1302" s="10">
+        <v>4</v>
+      </c>
+      <c r="E1302" s="11"/>
+      <c r="F1302" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1302" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1302" s="32"/>
+    </row>
+    <row r="1303" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1303" s="23">
+        <v>69716</v>
+      </c>
+      <c r="B1303" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1303" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1303" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1303" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1303" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1303" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1303" s="32"/>
+    </row>
+    <row r="1304" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1304" s="23">
+        <v>69977</v>
+      </c>
+      <c r="B1304" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1304" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1304" s="10">
+        <v>11</v>
+      </c>
+      <c r="E1304" s="11"/>
+      <c r="F1304" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1304" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1304" s="32"/>
+    </row>
+    <row r="1305" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1305" s="23">
+        <v>69686</v>
+      </c>
+      <c r="B1305" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1305" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1305" s="10">
+        <v>7</v>
+      </c>
+      <c r="E1305" s="11"/>
+      <c r="F1305" s="33"/>
+      <c r="G1305" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1305" s="32"/>
+    </row>
+    <row r="1306" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1306" s="23">
+        <v>70255</v>
+      </c>
+      <c r="B1306" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1306" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1306" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1306" s="11"/>
+      <c r="F1306" s="33"/>
+      <c r="G1306" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1306" s="32"/>
+    </row>
+    <row r="1307" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1307" s="9">
+        <v>70150</v>
+      </c>
+      <c r="B1307" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1307" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1307" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1307" s="11"/>
+      <c r="F1307" s="33"/>
+      <c r="G1307" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1307" s="32"/>
+    </row>
+    <row r="1308" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1308" s="23">
+        <v>69801</v>
+      </c>
+      <c r="B1308" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1308" s="14">
+        <v>46322</v>
+      </c>
+      <c r="D1308" s="10">
+        <v>15</v>
+      </c>
+      <c r="E1308" s="11"/>
+      <c r="F1308" s="33"/>
+      <c r="G1308" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1308" s="32"/>
+    </row>
+    <row r="1309" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1309" s="23">
+        <v>70628</v>
+      </c>
+      <c r="B1309" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1309" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1309" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1309" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1309" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1309" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1309" s="32"/>
+    </row>
+    <row r="1310" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1310" s="9">
+        <v>70879</v>
+      </c>
+      <c r="B1310" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1310" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1310" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1310" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1310" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1310" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1310" s="32"/>
+    </row>
+    <row r="1311" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1311" s="9">
+        <v>70880</v>
+      </c>
+      <c r="B1311" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1311" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1311" s="10">
+        <v>2</v>
+      </c>
+      <c r="E1311" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1311" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1311" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1311" s="32"/>
+    </row>
+    <row r="1312" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1312" s="9">
+        <v>70884</v>
+      </c>
+      <c r="B1312" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1312" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1312" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1312" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1312" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1312" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1312" s="32"/>
+    </row>
+    <row r="1313" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1313" s="9">
+        <v>70851</v>
+      </c>
+      <c r="B1313" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1313" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1313" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1313" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1313" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1313" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1313" s="32"/>
+    </row>
+    <row r="1314" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1314" s="23">
+        <v>70821</v>
+      </c>
+      <c r="B1314" s="13"/>
+      <c r="C1314" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1314" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1314" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1314" s="33"/>
+      <c r="G1314" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1314" s="32"/>
+    </row>
+    <row r="1315" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1315" s="9">
+        <v>69182</v>
+      </c>
+      <c r="B1315" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1315" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1315" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1315" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1315" s="33"/>
+      <c r="G1315" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1315" s="32"/>
+    </row>
+    <row r="1316" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1316" s="23">
+        <v>70242</v>
+      </c>
+      <c r="B1316" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1316" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1316" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1316" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1316" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1316" s="24"/>
+      <c r="H1316" s="32"/>
+    </row>
+    <row r="1317" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1317" s="9">
+        <v>70581</v>
+      </c>
+      <c r="B1317" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1317" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1317" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1317" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1317" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1317" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1317" s="32"/>
+    </row>
+    <row r="1318" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1318" s="9">
+        <v>69606</v>
+      </c>
+      <c r="B1318" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1318" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1318" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1318" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1318" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1318" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1318" s="32"/>
+    </row>
+    <row r="1319" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1319" s="23">
+        <v>69980</v>
+      </c>
+      <c r="B1319" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1319" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1319" s="10">
+        <v>2</v>
+      </c>
+      <c r="E1319" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1319" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1319" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1319" s="32"/>
+    </row>
+    <row r="1320" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1320" s="23">
+        <v>70299</v>
+      </c>
+      <c r="B1320" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1320" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1320" s="10">
+        <v>4</v>
+      </c>
+      <c r="E1320" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1320" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1320" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1320" s="32"/>
+    </row>
+    <row r="1321" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1321" s="23">
+        <v>70230</v>
+      </c>
+      <c r="B1321" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1321" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1321" s="10">
+        <v>4</v>
+      </c>
+      <c r="E1321" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1321" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1321" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1321" s="32"/>
+    </row>
+    <row r="1322" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1322" s="23">
+        <v>70268</v>
+      </c>
+      <c r="B1322" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1322" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1322" s="10">
+        <v>4</v>
+      </c>
+      <c r="E1322" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1322" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1322" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1322" s="32"/>
+    </row>
+    <row r="1323" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1323" s="23">
+        <v>70249</v>
+      </c>
+      <c r="B1323" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1323" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1323" s="10">
+        <v>6</v>
+      </c>
+      <c r="E1323" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1323" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1323" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1323" s="32"/>
+    </row>
+    <row r="1324" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1324" s="23">
+        <v>70182</v>
+      </c>
+      <c r="B1324" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1324" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1324" s="10">
+        <v>14</v>
+      </c>
+      <c r="E1324" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1324" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1324" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1324" s="32"/>
+    </row>
+    <row r="1325" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1325" s="23">
+        <v>70094</v>
+      </c>
+      <c r="B1325" s="13"/>
+      <c r="C1325" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1325" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1325" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1325" s="33"/>
+      <c r="G1325" s="24"/>
+      <c r="H1325" s="32"/>
+    </row>
+    <row r="1326" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1326" s="23">
+        <v>70034</v>
+      </c>
+      <c r="B1326" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1326" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1326" s="10">
+        <v>2</v>
+      </c>
+      <c r="E1326" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1326" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1326" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1326" s="32"/>
+    </row>
+    <row r="1327" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1327" s="23">
+        <v>70283</v>
+      </c>
+      <c r="B1327" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1327" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1327" s="10">
+        <v>6</v>
+      </c>
+      <c r="E1327" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1327" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1327" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1327" s="32"/>
+    </row>
+    <row r="1328" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1328" s="23">
+        <v>70285</v>
+      </c>
+      <c r="B1328" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1328" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1328" s="10">
+        <v>4</v>
+      </c>
+      <c r="E1328" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1328" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1328" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1328" s="32"/>
+    </row>
+    <row r="1329" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1329" s="23">
+        <v>70490</v>
+      </c>
+      <c r="B1329" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1329" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1329" s="10">
+        <v>2</v>
+      </c>
+      <c r="E1329" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1329" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1329" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1329" s="32"/>
+    </row>
+    <row r="1330" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1330" s="23">
+        <v>70048</v>
+      </c>
+      <c r="B1330" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1330" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1330" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1330" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1330" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1330" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1330" s="32"/>
+    </row>
+    <row r="1331" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1331" s="23">
+        <v>70017</v>
+      </c>
+      <c r="B1331" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1331" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1331" s="10">
+        <v>12</v>
+      </c>
+      <c r="E1331" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1331" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1331" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1331" s="32"/>
+    </row>
+    <row r="1332" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1332" s="23">
+        <v>69819</v>
+      </c>
+      <c r="B1332" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1332" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1332" s="10">
+        <v>14</v>
+      </c>
+      <c r="E1332" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1332" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1332" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1332" s="32"/>
+    </row>
+    <row r="1333" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1333" s="23">
+        <v>69177</v>
+      </c>
+      <c r="B1333" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1333" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1333" s="10">
+        <v>11</v>
+      </c>
+      <c r="E1333" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1333" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1333" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1333" s="32"/>
+    </row>
+    <row r="1334" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1334" s="23">
+        <v>69917</v>
+      </c>
+      <c r="B1334" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1334" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1334" s="10">
+        <v>8</v>
+      </c>
+      <c r="E1334" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1334" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1334" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1334" s="32"/>
+    </row>
+    <row r="1335" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1335" s="23">
+        <v>69577</v>
+      </c>
+      <c r="B1335" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1335" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1335" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1335" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1335" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1335" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1335" s="32"/>
+    </row>
+    <row r="1336" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1336" s="23">
+        <v>69824</v>
+      </c>
+      <c r="B1336" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1336" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1336" s="10">
+        <v>4</v>
+      </c>
+      <c r="E1336" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1336" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1336" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1336" s="32"/>
+    </row>
+    <row r="1337" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1337" s="23">
+        <v>69800</v>
+      </c>
+      <c r="B1337" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1337" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1337" s="10">
+        <v>2</v>
+      </c>
+      <c r="E1337" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1337" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1337" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1337" s="32"/>
+    </row>
+    <row r="1338" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1338" s="23">
+        <v>69573</v>
+      </c>
+      <c r="B1338" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1338" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1338" s="10">
+        <v>10</v>
+      </c>
+      <c r="E1338" s="11"/>
+      <c r="F1338" s="33"/>
+      <c r="G1338" s="24"/>
+      <c r="H1338" s="32"/>
+    </row>
+    <row r="1339" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1339" s="23">
+        <v>70025</v>
+      </c>
+      <c r="B1339" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1339" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1339" s="10">
+        <v>7</v>
+      </c>
+      <c r="E1339" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1339" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1339" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1339" s="32"/>
+    </row>
+    <row r="1340" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1340" s="23">
+        <v>70010</v>
+      </c>
+      <c r="B1340" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1340" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1340" s="10">
+        <v>9</v>
+      </c>
+      <c r="E1340" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1340" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1340" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1340" s="32"/>
+    </row>
+    <row r="1341" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1341" s="23">
+        <v>69717</v>
+      </c>
+      <c r="B1341" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1341" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1341" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1341" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1341" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1341" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1341" s="32"/>
+    </row>
+    <row r="1342" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1342" s="23">
+        <v>69746</v>
+      </c>
+      <c r="B1342" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1342" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1342" s="10">
+        <v>12</v>
+      </c>
+      <c r="E1342" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1342" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1342" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1342" s="32"/>
+    </row>
+    <row r="1343" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1343" s="23">
+        <v>70574</v>
+      </c>
+      <c r="B1343" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1343" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1343" s="10">
+        <v>11</v>
+      </c>
+      <c r="E1343" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1343" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1343" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1343" s="32"/>
+    </row>
+    <row r="1344" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1344" s="23">
+        <v>68538</v>
+      </c>
+      <c r="B1344" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1344" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1344" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1344" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1344" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1344" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1344" s="32"/>
+    </row>
+    <row r="1345" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1345" s="9">
+        <v>67067</v>
+      </c>
+      <c r="B1345" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1345" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1345" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1345" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1345" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1345" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1345" s="32"/>
+    </row>
+    <row r="1346" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1346" s="9">
+        <v>70640</v>
+      </c>
+      <c r="B1346" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1346" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1346" s="10">
+        <v>26</v>
+      </c>
+      <c r="E1346" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1346" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1346" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1346" s="32"/>
+    </row>
+    <row r="1347" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1347" s="9">
+        <v>70572</v>
+      </c>
+      <c r="B1347" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1347" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1347" s="10">
+        <v>8</v>
+      </c>
+      <c r="E1347" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1347" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1347" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1347" s="32"/>
+    </row>
+    <row r="1348" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1348" s="9">
+        <v>70540</v>
+      </c>
+      <c r="B1348" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1348" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1348" s="10">
+        <v>5</v>
+      </c>
+      <c r="E1348" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1348" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1348" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1348" s="32"/>
+    </row>
+    <row r="1349" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1349" s="23">
+        <v>69763</v>
+      </c>
+      <c r="B1349" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1349" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D1349" s="10">
+        <v>14</v>
+      </c>
+      <c r="E1349" s="11"/>
+      <c r="F1349" s="33"/>
+      <c r="G1349" s="24"/>
+      <c r="H1349" s="32"/>
+    </row>
+    <row r="1350" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1350" s="9">
+        <v>70679</v>
+      </c>
+      <c r="B1350" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1350" s="41">
+        <v>46323</v>
+      </c>
+      <c r="D1350" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1350" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1350" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1350" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1350" s="32"/>
+    </row>
+    <row r="1351" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1351" s="9">
+        <v>70938</v>
+      </c>
+      <c r="B1351" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1351" s="41">
+        <v>46323</v>
+      </c>
+      <c r="D1351" s="10">
+        <v>0</v>
+      </c>
+      <c r="E1351" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1351" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1351" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1351" s="32"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
@@ -34994,7 +36790,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="str" cm="1">
-        <f t="array" ref="A1:A20">_xlfn.UNIQUE(DadosBrutos!C1:C1273)</f>
+        <f t="array" ref="A1:A21">_xlfn.UNIQUE(DadosBrutos!C1:C1351)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="19" t="s">
@@ -35169,11 +36965,17 @@
       </c>
       <c r="B20" s="18">
         <f>COUNTIF(DadosBrutos!C:C, A20)</f>
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="A21" s="20">
+        <v>46323</v>
+      </c>
+      <c r="B21" s="18">
+        <f>COUNTIF(DadosBrutos!C:C, A21)</f>
+        <v>43</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>
@@ -37311,7 +39113,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="str" cm="1">
-        <f t="array" ref="A1:A20">_xlfn.UNIQUE(DadosBrutos!C1:C1273)</f>
+        <f t="array" ref="A1:A21">_xlfn.UNIQUE(DadosBrutos!C1:C1351)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="19" t="s">
@@ -37565,11 +39367,21 @@
       </c>
       <c r="C20">
         <f>COUNTIFS(DadosBrutos!C:C, A20, DadosBrutos!G:G, "BACKLOG")</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="A21" s="20">
+        <v>46323</v>
+      </c>
+      <c r="B21">
+        <f>COUNTIFS(DadosBrutos!C:C, A21, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <f>COUNTIFS(DadosBrutos!C:C, A21, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>34</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>

--- a/DadosProducao.xlsx
+++ b/DadosProducao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DA2579-E3AF-4DF4-841B-19C782F3D05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDFEE1B-A80A-4FD2-87F2-01603E89F013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5280" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5311" uniqueCount="61">
   <si>
     <t>PV</t>
   </si>
@@ -591,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -654,6 +654,7 @@
     <xf numFmtId="14" fontId="6" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -33526,32 +33527,40 @@
     </row>
     <row r="1376" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1376" s="9">
-        <v>70891</v>
-      </c>
-      <c r="B1376" s="12"/>
+        <v>70943</v>
+      </c>
+      <c r="B1376" s="35" t="s">
+        <v>56</v>
+      </c>
       <c r="C1376" s="28">
         <v>46323</v>
       </c>
       <c r="D1376" s="10">
-        <v>3</v>
-      </c>
-      <c r="E1376" s="11"/>
-      <c r="F1376" s="31"/>
-      <c r="G1376" s="23"/>
+        <v>5</v>
+      </c>
+      <c r="E1376" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1376" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1376" s="16" t="s">
+        <v>11</v>
+      </c>
       <c r="H1376" s="40"/>
     </row>
     <row r="1377" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1377" s="9">
-        <v>70943</v>
+        <v>70106</v>
       </c>
       <c r="B1377" s="35" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C1377" s="28">
         <v>46323</v>
       </c>
       <c r="D1377" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E1377" s="11" t="s">
         <v>9</v>
@@ -33565,52 +33574,68 @@
       <c r="H1377" s="40"/>
     </row>
     <row r="1378" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1378" s="9">
-        <v>70940</v>
-      </c>
-      <c r="B1378" s="12"/>
+      <c r="A1378" s="22">
+        <v>69914</v>
+      </c>
+      <c r="B1378" s="35" t="s">
+        <v>55</v>
+      </c>
       <c r="C1378" s="28">
         <v>46323</v>
       </c>
       <c r="D1378" s="10">
-        <v>2</v>
-      </c>
-      <c r="E1378" s="11"/>
-      <c r="F1378" s="31"/>
-      <c r="G1378" s="23"/>
+        <v>6</v>
+      </c>
+      <c r="E1378" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1378" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1378" s="16" t="s">
+        <v>11</v>
+      </c>
       <c r="H1378" s="40"/>
     </row>
     <row r="1379" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1379" s="9">
-        <v>70106</v>
-      </c>
-      <c r="B1379" s="12"/>
+        <v>69584</v>
+      </c>
+      <c r="B1379" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="C1379" s="28">
         <v>46323</v>
       </c>
       <c r="D1379" s="10">
         <v>0</v>
       </c>
-      <c r="E1379" s="11"/>
-      <c r="F1379" s="31"/>
-      <c r="G1379" s="23"/>
+      <c r="E1379" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1379" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1379" s="16" t="s">
+        <v>11</v>
+      </c>
       <c r="H1379" s="40"/>
     </row>
     <row r="1380" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1380" s="22">
-        <v>69914</v>
+      <c r="A1380" s="9">
+        <v>70931</v>
       </c>
       <c r="B1380" s="35" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C1380" s="28">
         <v>46323</v>
       </c>
       <c r="D1380" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1380" s="11" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F1380" s="36" t="s">
         <v>59</v>
@@ -33622,22 +33647,22 @@
     </row>
     <row r="1381" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1381" s="9">
-        <v>69584</v>
-      </c>
-      <c r="B1381" s="12" t="s">
-        <v>58</v>
+        <v>70954</v>
+      </c>
+      <c r="B1381" s="35" t="s">
+        <v>30</v>
       </c>
       <c r="C1381" s="28">
         <v>46323</v>
       </c>
       <c r="D1381" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1381" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1381" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="F1381" s="36" t="s">
+        <v>59</v>
       </c>
       <c r="G1381" s="16" t="s">
         <v>11</v>
@@ -33645,352 +33670,381 @@
       <c r="H1381" s="40"/>
     </row>
     <row r="1382" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1382" s="9">
-        <v>69736</v>
-      </c>
-      <c r="B1382" s="12"/>
-      <c r="C1382" s="28">
+      <c r="A1382" s="22">
+        <v>68159</v>
+      </c>
+      <c r="B1382" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1382" s="13">
         <v>46323</v>
       </c>
       <c r="D1382" s="10">
         <v>0</v>
       </c>
-      <c r="E1382" s="11"/>
-      <c r="F1382" s="31"/>
-      <c r="G1382" s="23"/>
+      <c r="E1382" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1382" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1382" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="H1382" s="40"/>
     </row>
     <row r="1383" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1383" s="9">
-        <v>70828</v>
-      </c>
-      <c r="B1383" s="12"/>
-      <c r="C1383" s="28">
+      <c r="A1383" s="22">
+        <v>68156</v>
+      </c>
+      <c r="B1383" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1383" s="13">
         <v>46323</v>
       </c>
       <c r="D1383" s="10">
-        <v>5</v>
-      </c>
-      <c r="E1383" s="11"/>
-      <c r="F1383" s="31"/>
-      <c r="G1383" s="23"/>
+        <v>1</v>
+      </c>
+      <c r="E1383" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1383" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1383" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="H1383" s="40"/>
     </row>
     <row r="1384" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1384" s="9">
-        <v>70960</v>
-      </c>
-      <c r="B1384" s="12"/>
-      <c r="C1384" s="28">
+      <c r="A1384" s="22">
+        <v>70067</v>
+      </c>
+      <c r="B1384" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1384" s="13">
         <v>46323</v>
       </c>
       <c r="D1384" s="10">
-        <v>3</v>
-      </c>
-      <c r="E1384" s="11"/>
-      <c r="F1384" s="31"/>
-      <c r="G1384" s="23"/>
+        <v>0</v>
+      </c>
+      <c r="E1384" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1384" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1384" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="H1384" s="40"/>
     </row>
     <row r="1385" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1385" s="9">
-        <v>70945</v>
-      </c>
-      <c r="B1385" s="12"/>
-      <c r="C1385" s="28">
+        <v>69572</v>
+      </c>
+      <c r="B1385" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1385" s="13">
         <v>46323</v>
       </c>
       <c r="D1385" s="10">
-        <v>3</v>
-      </c>
-      <c r="E1385" s="11"/>
-      <c r="F1385" s="31"/>
-      <c r="G1385" s="23"/>
+        <v>0</v>
+      </c>
+      <c r="E1385" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1385" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1385" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="H1385" s="40"/>
     </row>
     <row r="1386" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1386" s="9">
-        <v>70927</v>
-      </c>
-      <c r="B1386" s="12"/>
-      <c r="C1386" s="28">
+      <c r="A1386" s="22">
+        <v>70699</v>
+      </c>
+      <c r="B1386" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1386" s="13">
         <v>46323</v>
       </c>
       <c r="D1386" s="10">
-        <v>7</v>
-      </c>
-      <c r="E1386" s="11"/>
-      <c r="F1386" s="31"/>
-      <c r="G1386" s="23"/>
+        <v>1</v>
+      </c>
+      <c r="E1386" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1386" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1386" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="H1386" s="40"/>
     </row>
     <row r="1387" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1387" s="9">
-        <v>70931</v>
-      </c>
-      <c r="B1387" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1387" s="28">
+      <c r="A1387" s="22">
+        <v>69388</v>
+      </c>
+      <c r="B1387" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1387" s="13">
         <v>46323</v>
       </c>
       <c r="D1387" s="10">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E1387" s="11" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F1387" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G1387" s="16" t="s">
-        <v>11</v>
+      <c r="G1387" s="15" t="s">
+        <v>14</v>
       </c>
       <c r="H1387" s="40"/>
     </row>
     <row r="1388" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1388" s="9">
-        <v>70954</v>
+        <v>71052</v>
       </c>
       <c r="B1388" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1388" s="28">
+        <v>58</v>
+      </c>
+      <c r="C1388" s="13">
         <v>46323</v>
       </c>
       <c r="D1388" s="10">
-        <v>1</v>
-      </c>
-      <c r="E1388" s="11" t="s">
-        <v>26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E1388" s="11"/>
       <c r="F1388" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G1388" s="16" t="s">
-        <v>11</v>
+      <c r="G1388" s="15" t="s">
+        <v>14</v>
       </c>
       <c r="H1388" s="40"/>
     </row>
     <row r="1389" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1389" s="22">
-        <v>70195</v>
-      </c>
-      <c r="B1389" s="12"/>
-      <c r="C1389" s="28">
+      <c r="A1389" s="9">
+        <v>70517</v>
+      </c>
+      <c r="B1389" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1389" s="13">
         <v>46323</v>
       </c>
       <c r="D1389" s="10">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E1389" s="11"/>
-      <c r="F1389" s="31"/>
-      <c r="G1389" s="23"/>
+      <c r="F1389" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1389" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="H1389" s="40"/>
     </row>
     <row r="1390" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1390" s="22">
-        <v>68242</v>
-      </c>
-      <c r="B1390" s="12"/>
-      <c r="C1390" s="28">
-        <v>46323</v>
+      <c r="A1390" s="9">
+        <v>70924</v>
+      </c>
+      <c r="B1390" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1390" s="42">
+        <v>46324</v>
       </c>
       <c r="D1390" s="10">
+        <v>17</v>
+      </c>
+      <c r="E1390" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1390" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1390" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1391" s="9">
+        <v>70586</v>
+      </c>
+      <c r="B1391" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1391" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1391" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1391" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1391" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1391" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1392" s="9">
+        <v>70858</v>
+      </c>
+      <c r="B1392" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1392" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1392" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1392" s="11"/>
+      <c r="F1392" s="31"/>
+      <c r="G1392" s="23"/>
+    </row>
+    <row r="1393" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1393" s="9">
+        <v>70885</v>
+      </c>
+      <c r="B1393" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1393" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1393" s="10">
+        <v>1</v>
+      </c>
+      <c r="E1393" s="11"/>
+      <c r="F1393" s="31"/>
+      <c r="G1393" s="23"/>
+    </row>
+    <row r="1394" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1394" s="9">
+        <v>70862</v>
+      </c>
+      <c r="B1394" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1394" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1394" s="10">
+        <v>5</v>
+      </c>
+      <c r="E1394" s="11"/>
+      <c r="F1394" s="31"/>
+      <c r="G1394" s="23"/>
+    </row>
+    <row r="1395" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1395" s="9">
+        <v>65955</v>
+      </c>
+      <c r="B1395" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1395" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1395" s="10">
         <v>0</v>
       </c>
-      <c r="E1390" s="11"/>
-      <c r="F1390" s="31"/>
-      <c r="G1390" s="23"/>
-      <c r="H1390" s="40"/>
-    </row>
-    <row r="1391" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1391" s="22">
-        <v>68159</v>
-      </c>
-      <c r="B1391" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1391" s="13">
-        <v>46323</v>
-      </c>
-      <c r="D1391" s="10">
+      <c r="E1395" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1395" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1395" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1396" s="9">
+        <v>70617</v>
+      </c>
+      <c r="B1396" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1396" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1396" s="10">
         <v>0</v>
       </c>
-      <c r="E1391" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1391" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1391" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1391" s="40"/>
-    </row>
-    <row r="1392" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1392" s="22">
-        <v>68156</v>
-      </c>
-      <c r="B1392" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1392" s="13">
-        <v>46323</v>
-      </c>
-      <c r="D1392" s="10">
-        <v>1</v>
-      </c>
-      <c r="E1392" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1392" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1392" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1392" s="40"/>
-    </row>
-    <row r="1393" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1393" s="22">
-        <v>70067</v>
-      </c>
-      <c r="B1393" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1393" s="13">
-        <v>46323</v>
-      </c>
-      <c r="D1393" s="10">
-        <v>0</v>
-      </c>
-      <c r="E1393" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1393" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1393" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1393" s="40"/>
-    </row>
-    <row r="1394" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1394" s="9">
-        <v>69572</v>
-      </c>
-      <c r="B1394" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1394" s="13">
-        <v>46323</v>
-      </c>
-      <c r="D1394" s="10">
-        <v>0</v>
-      </c>
-      <c r="E1394" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1394" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1394" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1394" s="40"/>
-    </row>
-    <row r="1395" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1395" s="22">
-        <v>70699</v>
-      </c>
-      <c r="B1395" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1395" s="13">
-        <v>46323</v>
-      </c>
-      <c r="D1395" s="10">
-        <v>1</v>
-      </c>
-      <c r="E1395" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1395" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1395" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1395" s="40"/>
-    </row>
-    <row r="1396" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1396" s="22">
-        <v>69388</v>
-      </c>
-      <c r="B1396" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1396" s="13">
-        <v>46323</v>
-      </c>
-      <c r="D1396" s="10">
-        <v>24</v>
-      </c>
       <c r="E1396" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F1396" s="36" t="s">
-        <v>59</v>
+      <c r="F1396" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="G1396" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H1396" s="40"/>
-    </row>
-    <row r="1397" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1397" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1397" s="9">
-        <v>71052</v>
-      </c>
-      <c r="B1397" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1397" s="13">
-        <v>46323</v>
+        <v>69007</v>
+      </c>
+      <c r="B1397" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1397" s="42">
+        <v>46324</v>
       </c>
       <c r="D1397" s="10">
         <v>0</v>
       </c>
-      <c r="E1397" s="11"/>
-      <c r="F1397" s="36" t="s">
-        <v>59</v>
+      <c r="E1397" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1397" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="G1397" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H1397" s="40"/>
-    </row>
-    <row r="1398" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="1398" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1398" s="9">
-        <v>70517</v>
-      </c>
-      <c r="B1398" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1398" s="13">
-        <v>46323</v>
+        <v>69022</v>
+      </c>
+      <c r="B1398" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1398" s="42">
+        <v>46324</v>
       </c>
       <c r="D1398" s="10">
-        <v>7</v>
-      </c>
-      <c r="E1398" s="11"/>
-      <c r="F1398" s="36" t="s">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="E1398" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1398" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="G1398" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H1398" s="40"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
@@ -34025,7 +34079,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="str" cm="1">
-        <f t="array" ref="A1:A21">_xlfn.UNIQUE(DadosBrutos!C1:C1398)</f>
+        <f t="array" ref="A1:A22">_xlfn.UNIQUE(DadosBrutos!C1:C1398)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="18" t="s">
@@ -34209,11 +34263,17 @@
       </c>
       <c r="B21" s="17">
         <f>COUNTIF(DadosBrutos!C:C, A21)</f>
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="A22" s="19">
+        <v>46324</v>
+      </c>
+      <c r="B22" s="17">
+        <f>COUNTIF(DadosBrutos!C:C, A22)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="19"/>
@@ -36348,7 +36408,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="str" cm="1">
-        <f t="array" ref="A1:A21">_xlfn.UNIQUE(DadosBrutos!C1:C1398)</f>
+        <f t="array" ref="A1:A22">_xlfn.UNIQUE(DadosBrutos!C1:C1398)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="18" t="s">
@@ -36615,11 +36675,21 @@
       </c>
       <c r="C21">
         <f>COUNTIFS(DadosBrutos!C:C, A21, DadosBrutos!G:G, "BACKLOG")</f>
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="A22" s="19">
+        <v>46324</v>
+      </c>
+      <c r="B22">
+        <f>COUNTIFS(DadosBrutos!C:C, A22, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <f>COUNTIFS(DadosBrutos!C:C, A22, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="19"/>

--- a/DadosProducao.xlsx
+++ b/DadosProducao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E543773D-807A-423F-871F-5C20919AC0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD622773-408F-466A-858F-C9E537EE1F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{3AA6C56D-DA97-499B-A05C-D9170B04DAB1}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5503" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5646" uniqueCount="59">
   <si>
     <t>PV</t>
   </si>
@@ -355,7 +355,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,6 +449,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1188FF"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -571,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -638,6 +644,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1047,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B0C76F-2D49-44D6-9EF1-05536D6E01AD}">
-  <dimension ref="A1:G1457"/>
+  <dimension ref="A1:H1477"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -32189,16 +32199,24 @@
       <c r="A1375" s="35">
         <v>70891</v>
       </c>
-      <c r="B1375" s="10"/>
+      <c r="B1375" s="40" t="s">
+        <v>34</v>
+      </c>
       <c r="C1375" s="25">
         <v>46324</v>
       </c>
       <c r="D1375" s="8">
         <v>3</v>
       </c>
-      <c r="E1375" s="9"/>
-      <c r="F1375" s="28"/>
-      <c r="G1375" s="20"/>
+      <c r="E1375" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1375" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1375" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1376" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1376" s="35">
@@ -32342,7 +32360,9 @@
       <c r="A1382" s="35">
         <v>70828</v>
       </c>
-      <c r="B1382" s="10"/>
+      <c r="B1382" s="30" t="s">
+        <v>15</v>
+      </c>
       <c r="C1382" s="25">
         <v>46324</v>
       </c>
@@ -32350,23 +32370,35 @@
         <v>5</v>
       </c>
       <c r="E1382" s="9"/>
-      <c r="F1382" s="28"/>
-      <c r="G1382" s="20"/>
+      <c r="F1382" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1382" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1383" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1383" s="35">
         <v>70960</v>
       </c>
-      <c r="B1383" s="10"/>
+      <c r="B1383" s="40" t="s">
+        <v>34</v>
+      </c>
       <c r="C1383" s="25">
         <v>46324</v>
       </c>
       <c r="D1383" s="8">
         <v>3</v>
       </c>
-      <c r="E1383" s="9"/>
-      <c r="F1383" s="28"/>
-      <c r="G1383" s="20"/>
+      <c r="E1383" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1383" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1383" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1384" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1384" s="35">
@@ -32387,7 +32419,9 @@
       <c r="A1385" s="35">
         <v>70927</v>
       </c>
-      <c r="B1385" s="10"/>
+      <c r="B1385" s="30" t="s">
+        <v>57</v>
+      </c>
       <c r="C1385" s="25">
         <v>46324</v>
       </c>
@@ -32395,8 +32429,12 @@
         <v>7</v>
       </c>
       <c r="E1385" s="9"/>
-      <c r="F1385" s="28"/>
-      <c r="G1385" s="20"/>
+      <c r="F1385" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1385" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1386" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1386" s="35">
@@ -32448,16 +32486,24 @@
       <c r="A1388" s="36">
         <v>70195</v>
       </c>
-      <c r="B1388" s="10"/>
-      <c r="C1388" s="25">
-        <v>46324</v>
+      <c r="B1388" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1388" s="11">
+        <v>46319</v>
       </c>
       <c r="D1388" s="8">
         <v>25</v>
       </c>
-      <c r="E1388" s="9"/>
-      <c r="F1388" s="28"/>
-      <c r="G1388" s="20"/>
+      <c r="E1388" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1388" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1388" s="13" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1389" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1389" s="36">
@@ -33137,7 +33183,9 @@
       <c r="A1419" s="35">
         <v>66748</v>
       </c>
-      <c r="B1419" s="10"/>
+      <c r="B1419" s="40" t="s">
+        <v>44</v>
+      </c>
       <c r="C1419" s="34">
         <v>46324</v>
       </c>
@@ -33147,8 +33195,8 @@
       <c r="E1419" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1419" s="12" t="s">
-        <v>26</v>
+      <c r="F1419" s="31" t="s">
+        <v>58</v>
       </c>
       <c r="G1419" s="13" t="s">
         <v>13</v>
@@ -33449,16 +33497,24 @@
       <c r="A1433" s="36">
         <v>70570</v>
       </c>
-      <c r="B1433" s="10"/>
+      <c r="B1433" s="30" t="s">
+        <v>35</v>
+      </c>
       <c r="C1433" s="25">
         <v>46324</v>
       </c>
       <c r="D1433" s="8">
         <v>17</v>
       </c>
-      <c r="E1433" s="9"/>
-      <c r="F1433" s="28"/>
-      <c r="G1433" s="20"/>
+      <c r="E1433" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1433" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1433" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1434" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1434" s="36">
@@ -33556,22 +33612,32 @@
       <c r="A1438" s="35">
         <v>70993</v>
       </c>
-      <c r="B1438" s="10"/>
+      <c r="B1438" s="40" t="s">
+        <v>44</v>
+      </c>
       <c r="C1438" s="25">
         <v>46324</v>
       </c>
       <c r="D1438" s="8">
         <v>2</v>
       </c>
-      <c r="E1438" s="9"/>
-      <c r="F1438" s="28"/>
-      <c r="G1438" s="20"/>
+      <c r="E1438" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1438" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1438" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1439" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1439" s="35">
         <v>70987</v>
       </c>
-      <c r="B1439" s="10"/>
+      <c r="B1439" s="40" t="s">
+        <v>44</v>
+      </c>
       <c r="C1439" s="25">
         <v>46324</v>
       </c>
@@ -33579,14 +33645,20 @@
         <v>3</v>
       </c>
       <c r="E1439" s="9"/>
-      <c r="F1439" s="28"/>
-      <c r="G1439" s="20"/>
+      <c r="F1439" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1439" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1440" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1440" s="35">
         <v>71053</v>
       </c>
-      <c r="B1440" s="10"/>
+      <c r="B1440" s="40" t="s">
+        <v>54</v>
+      </c>
       <c r="C1440" s="25">
         <v>46324</v>
       </c>
@@ -33594,14 +33666,20 @@
         <v>5</v>
       </c>
       <c r="E1440" s="9"/>
-      <c r="F1440" s="28"/>
-      <c r="G1440" s="20"/>
+      <c r="F1440" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1440" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1441" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1441" s="35">
         <v>70968</v>
       </c>
-      <c r="B1441" s="10"/>
+      <c r="B1441" s="30" t="s">
+        <v>15</v>
+      </c>
       <c r="C1441" s="25">
         <v>46324</v>
       </c>
@@ -33609,14 +33687,20 @@
         <v>4</v>
       </c>
       <c r="E1441" s="9"/>
-      <c r="F1441" s="28"/>
-      <c r="G1441" s="20"/>
+      <c r="F1441" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1441" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1442" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1442" s="35">
         <v>70908</v>
       </c>
-      <c r="B1442" s="10"/>
+      <c r="B1442" s="30" t="s">
+        <v>15</v>
+      </c>
       <c r="C1442" s="25">
         <v>46324</v>
       </c>
@@ -33624,14 +33708,20 @@
         <v>0</v>
       </c>
       <c r="E1442" s="9"/>
-      <c r="F1442" s="28"/>
-      <c r="G1442" s="20"/>
+      <c r="F1442" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1442" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1443" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1443" s="35">
         <v>69610</v>
       </c>
-      <c r="B1443" s="10"/>
+      <c r="B1443" s="40" t="s">
+        <v>35</v>
+      </c>
       <c r="C1443" s="25">
         <v>46324</v>
       </c>
@@ -33639,38 +33729,58 @@
         <v>0</v>
       </c>
       <c r="E1443" s="9"/>
-      <c r="F1443" s="28"/>
-      <c r="G1443" s="20"/>
+      <c r="F1443" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1443" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1444" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1444" s="35">
         <v>69035</v>
       </c>
-      <c r="B1444" s="10"/>
+      <c r="B1444" s="30" t="s">
+        <v>29</v>
+      </c>
       <c r="C1444" s="25">
         <v>46324</v>
       </c>
       <c r="D1444" s="8">
         <v>0</v>
       </c>
-      <c r="E1444" s="9"/>
-      <c r="F1444" s="28"/>
-      <c r="G1444" s="20"/>
+      <c r="E1444" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1444" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1444" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1445" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1445" s="35">
         <v>68253</v>
       </c>
-      <c r="B1445" s="10"/>
+      <c r="B1445" s="30" t="s">
+        <v>57</v>
+      </c>
       <c r="C1445" s="25">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D1445" s="8">
         <v>1</v>
       </c>
-      <c r="E1445" s="9"/>
-      <c r="F1445" s="28"/>
-      <c r="G1445" s="20"/>
+      <c r="E1445" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1445" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1445" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1446" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1446" s="35">
@@ -33699,7 +33809,9 @@
       <c r="A1447" s="36">
         <v>69606</v>
       </c>
-      <c r="B1447" s="10"/>
+      <c r="B1447" s="30" t="s">
+        <v>35</v>
+      </c>
       <c r="C1447" s="25">
         <v>46324</v>
       </c>
@@ -33707,14 +33819,20 @@
         <v>0</v>
       </c>
       <c r="E1447" s="9"/>
-      <c r="F1447" s="28"/>
-      <c r="G1447" s="20"/>
+      <c r="F1447" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1447" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1448" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1448" s="35">
         <v>66747</v>
       </c>
-      <c r="B1448" s="10"/>
+      <c r="B1448" s="30" t="s">
+        <v>54</v>
+      </c>
       <c r="C1448" s="25">
         <v>46324</v>
       </c>
@@ -33722,8 +33840,12 @@
         <v>0</v>
       </c>
       <c r="E1448" s="9"/>
-      <c r="F1448" s="28"/>
-      <c r="G1448" s="20"/>
+      <c r="F1448" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1448" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1449" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1449" s="36">
@@ -33752,7 +33874,9 @@
       <c r="A1450" s="35">
         <v>71025</v>
       </c>
-      <c r="B1450" s="10"/>
+      <c r="B1450" s="30" t="s">
+        <v>54</v>
+      </c>
       <c r="C1450" s="25">
         <v>46324</v>
       </c>
@@ -33760,38 +33884,58 @@
         <v>1</v>
       </c>
       <c r="E1450" s="9"/>
-      <c r="F1450" s="28"/>
-      <c r="G1450" s="20"/>
+      <c r="F1450" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1450" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1451" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1451" s="36">
         <v>70243</v>
       </c>
-      <c r="B1451" s="10"/>
+      <c r="B1451" s="32" t="s">
+        <v>55</v>
+      </c>
       <c r="C1451" s="25">
         <v>46324</v>
       </c>
       <c r="D1451" s="8">
         <v>0</v>
       </c>
-      <c r="E1451" s="9"/>
-      <c r="F1451" s="28"/>
-      <c r="G1451" s="20"/>
+      <c r="E1451" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1451" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1451" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1452" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1452" s="35">
         <v>66634</v>
       </c>
-      <c r="B1452" s="10"/>
+      <c r="B1452" s="40" t="s">
+        <v>35</v>
+      </c>
       <c r="C1452" s="25">
         <v>46324</v>
       </c>
       <c r="D1452" s="8">
         <v>0</v>
       </c>
-      <c r="E1452" s="9"/>
-      <c r="F1452" s="28"/>
-      <c r="G1452" s="20"/>
+      <c r="E1452" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1452" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1452" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="1453" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1453" s="36">
@@ -33885,7 +34029,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1457" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1457" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1457" s="35">
         <v>71123</v>
       </c>
@@ -33907,6 +34051,478 @@
       <c r="G1457" s="13" t="s">
         <v>13</v>
       </c>
+    </row>
+    <row r="1458" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1458" s="35">
+        <v>71127</v>
+      </c>
+      <c r="B1458" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1458" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1458" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1458" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1458" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1458" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1458" s="41"/>
+    </row>
+    <row r="1459" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1459" s="35">
+        <v>71131</v>
+      </c>
+      <c r="B1459" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1459" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1459" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1459" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1459" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1459" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1459" s="41"/>
+    </row>
+    <row r="1460" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1460" s="36">
+        <v>69852</v>
+      </c>
+      <c r="B1460" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1460" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1460" s="8">
+        <v>3</v>
+      </c>
+      <c r="E1460" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1460" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1460" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1460" s="41"/>
+    </row>
+    <row r="1461" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1461" s="36">
+        <v>69416</v>
+      </c>
+      <c r="B1461" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1461" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1461" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1461" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1461" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1461" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1461" s="41"/>
+    </row>
+    <row r="1462" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1462" s="36">
+        <v>70644</v>
+      </c>
+      <c r="B1462" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1462" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1462" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1462" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1462" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1462" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1462" s="41"/>
+    </row>
+    <row r="1463" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1463" s="36">
+        <v>70048</v>
+      </c>
+      <c r="B1463" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1463" s="42">
+        <v>46324</v>
+      </c>
+      <c r="D1463" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1463" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1463" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1463" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1463" s="41"/>
+    </row>
+    <row r="1464" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1464" s="35">
+        <v>68253</v>
+      </c>
+      <c r="B1464" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1464" s="25">
+        <v>46325</v>
+      </c>
+      <c r="D1464" s="8">
+        <v>1</v>
+      </c>
+      <c r="E1464" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1464" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1464" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1464" s="41"/>
+    </row>
+    <row r="1465" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1465" s="35">
+        <v>70945</v>
+      </c>
+      <c r="B1465" s="10"/>
+      <c r="C1465" s="25">
+        <v>46325</v>
+      </c>
+      <c r="D1465" s="8">
+        <v>3</v>
+      </c>
+      <c r="E1465" s="9"/>
+      <c r="F1465" s="28"/>
+      <c r="G1465" s="20"/>
+      <c r="H1465" s="41"/>
+    </row>
+    <row r="1466" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1466" s="35">
+        <v>70616</v>
+      </c>
+      <c r="B1466" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1466" s="43">
+        <v>46325</v>
+      </c>
+      <c r="D1466" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1466" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1466" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1466" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1466" s="41"/>
+    </row>
+    <row r="1467" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1467" s="35">
+        <v>69480</v>
+      </c>
+      <c r="B1467" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1467" s="43">
+        <v>46325</v>
+      </c>
+      <c r="D1467" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1467" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1467" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1467" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1467" s="41"/>
+    </row>
+    <row r="1468" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1468" s="35">
+        <v>70608</v>
+      </c>
+      <c r="B1468" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1468" s="43">
+        <v>46325</v>
+      </c>
+      <c r="D1468" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1468" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1468" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1468" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1468" s="41"/>
+    </row>
+    <row r="1469" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1469" s="35">
+        <v>70513</v>
+      </c>
+      <c r="B1469" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1469" s="43">
+        <v>46325</v>
+      </c>
+      <c r="D1469" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1469" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1469" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1469" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1469" s="41"/>
+    </row>
+    <row r="1470" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1470" s="35">
+        <v>69421</v>
+      </c>
+      <c r="B1470" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1470" s="43">
+        <v>46325</v>
+      </c>
+      <c r="D1470" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1470" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1470" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1470" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1470" s="41"/>
+    </row>
+    <row r="1471" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1471" s="35">
+        <v>70853</v>
+      </c>
+      <c r="B1471" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1471" s="43">
+        <v>46325</v>
+      </c>
+      <c r="D1471" s="8">
+        <v>1</v>
+      </c>
+      <c r="E1471" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1471" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1471" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1471" s="41"/>
+    </row>
+    <row r="1472" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1472" s="35">
+        <v>70680</v>
+      </c>
+      <c r="B1472" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1472" s="43">
+        <v>46325</v>
+      </c>
+      <c r="D1472" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1472" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1472" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1472" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1472" s="41"/>
+    </row>
+    <row r="1473" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1473" s="35">
+        <v>70484</v>
+      </c>
+      <c r="B1473" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1473" s="43">
+        <v>46325</v>
+      </c>
+      <c r="D1473" s="8">
+        <v>0</v>
+      </c>
+      <c r="E1473" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1473" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1473" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1473" s="41"/>
+    </row>
+    <row r="1474" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1474" s="36">
+        <v>70835</v>
+      </c>
+      <c r="B1474" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1474" s="42">
+        <v>46325</v>
+      </c>
+      <c r="D1474" s="8">
+        <v>18</v>
+      </c>
+      <c r="E1474" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1474" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1474" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1474" s="41"/>
+    </row>
+    <row r="1475" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1475" s="35">
+        <v>71091</v>
+      </c>
+      <c r="B1475" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1475" s="42">
+        <v>46325</v>
+      </c>
+      <c r="D1475" s="8">
+        <v>8</v>
+      </c>
+      <c r="E1475" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1475" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1475" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1475" s="41"/>
+    </row>
+    <row r="1476" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1476" s="35">
+        <v>71092</v>
+      </c>
+      <c r="B1476" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1476" s="42">
+        <v>46325</v>
+      </c>
+      <c r="D1476" s="8">
+        <v>3</v>
+      </c>
+      <c r="E1476" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1476" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1476" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1476" s="41"/>
+    </row>
+    <row r="1477" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1477" s="35">
+        <v>71090</v>
+      </c>
+      <c r="B1477" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1477" s="42">
+        <v>46325</v>
+      </c>
+      <c r="D1477" s="8">
+        <v>6</v>
+      </c>
+      <c r="E1477" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1477" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1477" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1477" s="41"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
@@ -33941,7 +34557,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="str" cm="1">
-        <f t="array" ref="A1:A22">_xlfn.UNIQUE(DadosBrutos!C1:C1457)</f>
+        <f t="array" ref="A1:A23">_xlfn.UNIQUE(DadosBrutos!C1:C1477)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="16" t="s">
@@ -34107,7 +34723,7 @@
       </c>
       <c r="B19" s="15">
         <f>COUNTIF(DadosBrutos!C:C, A19)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -34134,11 +34750,17 @@
       </c>
       <c r="B22" s="15">
         <f>COUNTIF(DadosBrutos!C:C, A22)</f>
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
+      <c r="A23" s="17">
+        <v>46325</v>
+      </c>
+      <c r="B23" s="15">
+        <f>COUNTIF(DadosBrutos!C:C, A23)</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
@@ -36270,7 +36892,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="str" cm="1">
-        <f t="array" ref="A1:A22">_xlfn.UNIQUE(DadosBrutos!C1:C1457)</f>
+        <f t="array" ref="A1:A23">_xlfn.UNIQUE(DadosBrutos!C1:C1477)</f>
         <v>DATA</v>
       </c>
       <c r="B1" s="16" t="s">
@@ -36507,7 +37129,7 @@
       </c>
       <c r="B19">
         <f>COUNTIFS(DadosBrutos!C:C, A19, DadosBrutos!G:G, "SAUDAVEL")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <f>COUNTIFS(DadosBrutos!C:C, A19, DadosBrutos!G:G, "BACKLOG")</f>
@@ -36546,15 +37168,25 @@
       </c>
       <c r="B22">
         <f>COUNTIFS(DadosBrutos!C:C, A22, DadosBrutos!G:G, "SAUDAVEL")</f>
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <f>COUNTIFS(DadosBrutos!C:C, A22, DadosBrutos!G:G, "BACKLOG")</f>
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
+      <c r="A23" s="17">
+        <v>46325</v>
+      </c>
+      <c r="B23">
+        <f>COUNTIFS(DadosBrutos!C:C, A23, DadosBrutos!G:G, "SAUDAVEL")</f>
+        <v>12</v>
+      </c>
+      <c r="C23">
+        <f>COUNTIFS(DadosBrutos!C:C, A23, DadosBrutos!G:G, "BACKLOG")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
